--- a/saida/valuation_VALE3.xlsx
+++ b/saida/valuation_VALE3.xlsx
@@ -11,9 +11,9 @@
     <sheet name="Premissas" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Projeção" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="WACC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Múltiplos" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Múltiplos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Cenários" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
@@ -23,16 +23,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.0%;[Red]-0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0;[Red]-#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.00%;[Red]-0.00%"/>
+    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="169" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="#,##0.0"/>
+    <numFmt numFmtId="172" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="173" formatCode="0.0000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -85,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -120,46 +121,49 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -807,7 +811,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Entradas do modelo e seletor de cenário. Comece por aqui.</t>
+          <t>Os três cenários, o ajuste manual e as demais entradas. Comece por aqui.</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -843,12 +847,12 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>CAPM e custo médio ponderado de capital.</t>
+          <t>EV/EBITDA, P/L e P/VP contra as comparáveis.</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>Múltiplos</t>
         </is>
       </c>
     </row>
@@ -867,19 +871,19 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>EV/EBITDA, P/L e P/VP contra as comparáveis.</t>
+          <t>CAPM, custo médio ponderado de capital e o ajuste do cenário.</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Múltiplos</t>
+          <t>WACC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>Entradas e saídas de caixa e comparativo pessimista, base e otimista.</t>
+          <t>Entradas e saídas de caixa e comparativo pessimista, moderado e otimista.</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -900,11 +904,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:L60"/>
+  <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -943,7 +947,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -955,7 +959,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Número do cenário (1 pessimista, 2 base, 3 otimista)</t>
+          <t>Número do cenário (1 pessimista, 2 moderado, 3 otimista)</t>
         </is>
       </c>
       <c r="D5">
@@ -964,7 +968,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
@@ -978,842 +982,683 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Cenário base (editável)</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
+          <t>Variáveis de cenário</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Em uso</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>Partida 2026</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Pessimista</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Otimista</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste manual</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>De onde veio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Crescimento da receita, ao ano (2027 a 2030)</t>
+        </is>
+      </c>
+      <c r="C8" s="14">
+        <f>IF(ISNUMBER(H8),MIN(MAX(H8,MIN(E8:G8)),MAX(E8:G8)),CHOOSE($D$5,E8,F8,G8))</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026: nível dos últimos 12 meses (LTM 2T26). Pessimista: receita parada, ou seja, queda real. Moderado: inflação esperada no Focus para 2027-2030, crescimento real zero. Otimista: crescimento médio da receita de 2018 a 2025 (6.8% ao ano).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Margem EBITDA em 2030</t>
+        </is>
+      </c>
+      <c r="C9" s="14">
+        <f>IF(ISNUMBER(H9),MIN(MAX(H9,MIN(E9:G9)),MAX(E9:G9)),CHOOSE($D$5,E9,F9,G9))</f>
+        <v/>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026: nível dos últimos 12 meses (LTM 2T26). Daí até 2030 em linha reta. Faixa: margem EBITDA de 2021 a 2025, sem perdas por recuperabilidade. Pessimista é o segundo pior ano, moderado a mediana e otimista o segundo melhor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>WACC: pontos acima ou abaixo do CAPM</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>IF(ISNUMBER(H10),MIN(MAX(H10,MIN(E10:G10)),MAX(E10:G10)),CHOOSE($D$5,E10,F10,G10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Moderado: o WACC que sai do CAPM. O juro prefixado longo andou de 12.2% a 15.3% nos últimos dois anos; pessimista e otimista deslocam o WACC em metade dessa amplitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ajuste manual vazio = vale o cenário escolhido acima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Do cenário para cada ano (o que a projeção lê)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>2030E</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>De onde veio</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Crescimento do volume vendido</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Volume constante. A CVM não publica toneladas: usar o guidance da empresa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Variação do preço médio de venda</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>0.0209</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>0.0351</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2026: receita dos últimos 12 meses (LTM 2T26) sobre 2025. 2027 em diante: IPCA esperado no Focus (preço constante em termos reais).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Inflação dos custos e despesas</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>0.0206</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>0.0351</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2026: custo caixa dos últimos 12 meses sobre 2025. 2027 em diante: IPCA esperado no Focus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Outras receitas/despesas operacionais (% da receita)</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>-0.1739</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>-0.148</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>-0.122</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>-0.0961</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>-0.0701</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Equivalência patrimonial (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>-1570</v>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Mediana de 2021-2025, mantida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Investimento - capex (% da receita)</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>0.1449</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>0.1438</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>0.1427</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Depreciação (% do ativo fixo inicial)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>0.0569</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Mediana de 2021-2025, mantida.</t>
-        </is>
+          <t>Crescimento da receita</t>
+        </is>
+      </c>
+      <c r="D14" s="11">
+        <f>$D$8</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>$C$8</f>
+        <v/>
+      </c>
+      <c r="H14" s="11">
+        <f>$C$8</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de recebimento (dias)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>21.598</v>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Prazo de 2025, mantido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Prazo médio de estoque (dias)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>98.06699999999999</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>98.06699999999999</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>98.06699999999999</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>98.06699999999999</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>98.06699999999999</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Prazo de 2025, mantido.</t>
-        </is>
+          <t>Margem EBITDA</t>
+        </is>
+      </c>
+      <c r="D15" s="11">
+        <f>$D$9+($C$9-$D$9)*0/4</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>$D$9+($C$9-$D$9)*1/4</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>$D$9+($C$9-$D$9)*2/4</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>$D$9+($C$9-$D$9)*3/4</f>
+        <v/>
+      </c>
+      <c r="H15" s="11">
+        <f>$D$9+($C$9-$D$9)*4/4</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Prazo médio de pagamento (dias)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>91.9277</v>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>Prazo de 2025, mantido.</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Premissas iguais nos três cenários (editáveis)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>De onde veio</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Captação líquida de dívida (R$ milhões)</t>
+          <t>Despesas operacionais (% da receita)</t>
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0</v>
+        <v>0.0815</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>0</v>
+        <v>0.0785</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Dívida bruta mantida no nível de 2025.</t>
+          <t>Vendas, administrativas e outras, sem perdas por recuperabilidade. Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Equivalência patrimonial (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="H19" s="18" t="n">
+        <v>-1570</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Mediana de 2021-2025, mantida.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Choque dos cenários (soma ao cenário base)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Choque de 5% no preço em 2027, mantido depois. Ilustrativo.</t>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Investimento - capex (% da receita)</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.1449</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="G20" s="15" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>0.1415</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Do nível dos últimos 12 meses até a mediana de 2021-2025.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Crescimento do volume vendido - pessimista</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>0</v>
+          <t>Depreciação (% do ativo fixo inicial)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="G21" s="15" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Mediana de 2021-2025, mantida.</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Crescimento do volume vendido - otimista</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>0</v>
+          <t>Prazo médio de recebimento (dias)</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>21.598</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Prazo de 2025, mantido.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Variação do preço médio de venda - pessimista</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>0</v>
+          <t>Prazo médio de estoque (dias)</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>98.06699999999999</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>98.06699999999999</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>98.06699999999999</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>98.06699999999999</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>98.06699999999999</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Prazo de 2025, mantido.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Variação do preço médio de venda - otimista</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>0</v>
+          <t>Prazo médio de pagamento (dias)</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <v>91.9277</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Prazo de 2025, mantido.</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Inflação dos custos e despesas - pessimista</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="n">
+          <t>Captação líquida de dívida (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="14" t="n">
+      <c r="G25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="18" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Inflação dos custos e despesas - otimista</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Dívida bruta mantida no nível de 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Premissas gerais</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>De onde veio</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Premissas em uso (o que a projeção lê)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>2030E</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Alíquota de IR e CSLL</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Alíquota nominal: IRPJ 25% + CSLL 9%.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Crescimento do volume vendido</t>
-        </is>
-      </c>
-      <c r="D29" s="11">
-        <f>D8+CHOOSE($D$5,D21,0,D22)</f>
-        <v/>
-      </c>
-      <c r="E29" s="11">
-        <f>E8+CHOOSE($D$5,E21,0,E22)</f>
-        <v/>
-      </c>
-      <c r="F29" s="11">
-        <f>F8+CHOOSE($D$5,F21,0,F22)</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
-        <f>G8+CHOOSE($D$5,G21,0,G22)</f>
-        <v/>
-      </c>
-      <c r="H29" s="11">
-        <f>H8+CHOOSE($D$5,H21,0,H22)</f>
-        <v/>
+          <t>Custo da dívida antes do imposto (Kd)</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 17.8%.</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Variação do preço médio de venda</t>
-        </is>
-      </c>
-      <c r="D30" s="11">
-        <f>D9+CHOOSE($D$5,D23,0,D24)</f>
-        <v/>
-      </c>
-      <c r="E30" s="11">
-        <f>E9+CHOOSE($D$5,E23,0,E24)</f>
-        <v/>
-      </c>
-      <c r="F30" s="11">
-        <f>F9+CHOOSE($D$5,F23,0,F24)</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>G9+CHOOSE($D$5,G23,0,G24)</f>
-        <v/>
-      </c>
-      <c r="H30" s="11">
-        <f>H9+CHOOSE($D$5,H23,0,H24)</f>
-        <v/>
+          <t>Rendimento do caixa</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>0.0936</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Mediana 2023-2025 da receita financeira sobre o caixa médio.</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Inflação dos custos e despesas</t>
-        </is>
-      </c>
-      <c r="D31" s="11">
-        <f>D10+CHOOSE($D$5,D25,0,D26)</f>
-        <v/>
-      </c>
-      <c r="E31" s="11">
-        <f>E10+CHOOSE($D$5,E25,0,E26)</f>
-        <v/>
-      </c>
-      <c r="F31" s="11">
-        <f>F10+CHOOSE($D$5,F25,0,F26)</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>G10+CHOOSE($D$5,G25,0,G26)</f>
-        <v/>
-      </c>
-      <c r="H31" s="11">
-        <f>H10+CHOOSE($D$5,H25,0,H26)</f>
-        <v/>
+          <t>Dividendos (% do lucro)</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Mediana 2021-2025 de dividendos pagos sobre lucro, limitada a 0-100%.</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Outras receitas/despesas operacionais (% da receita)</t>
-        </is>
-      </c>
-      <c r="D32" s="11">
-        <f>D11</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>E11</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
-        <f>G11</f>
-        <v/>
-      </c>
-      <c r="H32" s="11">
-        <f>H11</f>
-        <v/>
+          <t>Juro sem risco (Rf)</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Tesouro prefixado de dez anos (em reais, nominal).</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Equivalência patrimonial (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D33" s="12">
-        <f>D12</f>
-        <v/>
-      </c>
-      <c r="E33" s="12">
-        <f>E12</f>
-        <v/>
-      </c>
-      <c r="F33" s="12">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="G33" s="12">
-        <f>G12</f>
-        <v/>
-      </c>
-      <c r="H33" s="12">
-        <f>H12</f>
-        <v/>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.7558</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.64.</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Investimento - capex (% da receita)</t>
-        </is>
-      </c>
-      <c r="D34" s="11">
-        <f>D13</f>
-        <v/>
-      </c>
-      <c r="E34" s="11">
-        <f>E13</f>
-        <v/>
-      </c>
-      <c r="F34" s="11">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="G34" s="11">
-        <f>G13</f>
-        <v/>
-      </c>
-      <c r="H34" s="11">
-        <f>H13</f>
-        <v/>
+          <t>Prêmio de risco de mercado</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Damodaran, mercado maduro. O risco-país já está no juro em reais.</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Depreciação (% do ativo fixo inicial)</t>
-        </is>
-      </c>
-      <c r="D35" s="11">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E35" s="11">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F35" s="11">
-        <f>F14</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="H35" s="11">
-        <f>H14</f>
-        <v/>
+          <t>Prêmio adicional (tamanho, risco específico)</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Sem prêmio adicional.</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de recebimento (dias)</t>
-        </is>
-      </c>
-      <c r="D36" s="17">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="E36" s="17">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="F36" s="17">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="G36" s="17">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="H36" s="17">
-        <f>H15</f>
-        <v/>
+          <t>Peso da dívida na estrutura de capital</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Dívida bruta do 2T26 sobre dívida mais valor de mercado.</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de estoque (dias)</t>
-        </is>
-      </c>
-      <c r="D37" s="17">
-        <f>D16</f>
-        <v/>
-      </c>
-      <c r="E37" s="17">
-        <f>E16</f>
-        <v/>
-      </c>
-      <c r="F37" s="17">
-        <f>F16</f>
-        <v/>
-      </c>
-      <c r="G37" s="17">
-        <f>G16</f>
-        <v/>
-      </c>
-      <c r="H37" s="17">
-        <f>H16</f>
-        <v/>
+          <t>Crescimento na perpetuidade (g)</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>IPCA esperado para 2030: crescimento real zero.</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de pagamento (dias)</t>
-        </is>
-      </c>
-      <c r="D38" s="17">
-        <f>D17</f>
-        <v/>
-      </c>
-      <c r="E38" s="17">
-        <f>E17</f>
-        <v/>
-      </c>
-      <c r="F38" s="17">
-        <f>F17</f>
-        <v/>
-      </c>
-      <c r="G38" s="17">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="H38" s="17">
-        <f>H17</f>
-        <v/>
+          <t>Capex na perpetuidade (múltiplo da depreciação)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Na perpetuidade a empresa reinveste o que deprecia.</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Captação líquida de dívida (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D39" s="12">
-        <f>D18</f>
-        <v/>
-      </c>
-      <c r="E39" s="12">
-        <f>E18</f>
-        <v/>
-      </c>
-      <c r="F39" s="12">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="G39" s="12">
-        <f>G18</f>
-        <v/>
-      </c>
-      <c r="H39" s="12">
-        <f>H18</f>
-        <v/>
+          <t>Outros passivos tratados como dívida (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Nenhum. Provisões (barragens, contingências) não entram como dívida.</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Premissas gerais</t>
+          <t>Dados de mercado e datas</t>
         </is>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -1828,292 +1673,102 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>De onde veio</t>
+          <t>Fonte</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Alíquota de IR e CSLL</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>0.34</v>
+          <t>Data-base do valuation</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>46203</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Alíquota nominal: IRPJ 25% + CSLL 9%.</t>
+          <t>Último ITR.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Custo da dívida antes do imposto (Kd)</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>0.1291</v>
+          <t>Fração de 2026 que ainda falta</t>
+        </is>
+      </c>
+      <c r="D43" s="23">
+        <f>(DATE(2026,12,31)-D42)/365</f>
+        <v/>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Piso: a taxa do Tesouro prefixado de dez anos, sem spread de crédito. Custo implícito mediano 2023-2025: 17.8%.</t>
+          <t>Só essa parte do fluxo de 2026 entra no valor.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Rendimento do caixa</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>0.0936</v>
+          <t>Ações em circulação (milhões)</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>4072.366</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Mediana 2023-2025 da receita financeira sobre o caixa médio.</t>
+          <t>CVM, composição do capital em 2026-06-30, sem tesouraria.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Dividendos (% do lucro)</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>0.679</v>
+          <t>Preço da ação (R$)</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="n">
+        <v>67.64</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Mediana 2021-2025 de dividendos pagos sobre lucro, limitada a 0-100%.</t>
+          <t>B3, fechamento de 2026-10-08.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Juro sem risco (Rf)</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>0.1291</v>
+          <t>Valor de mercado (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>275454.8362</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Tesouro prefixado de dez anos (em reais, nominal).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>0.7558</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Regressão de 5 anos, retornos semanais contra o BOVA11, preços sem ajuste de proventos. Beta de 2 anos: 0.64.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio de risco de mercado</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>0.0423</v>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Damodaran, mercado maduro. O risco-país já está no juro em reais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio adicional (tamanho, risco específico)</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>Sem prêmio adicional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Peso da dívida na estrutura de capital</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>0.2625</v>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>Dívida bruta do 2T26 sobre dívida mais valor de mercado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Crescimento na perpetuidade (g)</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>IPCA esperado para 2030: crescimento real zero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Capex na perpetuidade (múltiplo da depreciação)</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Na perpetuidade a empresa reinveste o que deprecia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Outros passivos tratados como dívida (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>Nenhum. Provisões (barragens, contingências) não entram como dívida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Dados de mercado e datas</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Data-base do valuation</t>
-        </is>
-      </c>
-      <c r="D56" s="20" t="n">
-        <v>46203</v>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>Último ITR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>Fração de 2026 que ainda falta</t>
-        </is>
-      </c>
-      <c r="D57" s="21">
-        <f>(DATE(2026,12,31)-D56)/365</f>
-        <v/>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>Só essa parte do fluxo de 2026 entra no valor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Ações em circulação (milhões)</t>
-        </is>
-      </c>
-      <c r="D58" s="22" t="n">
-        <v>4072.366</v>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>CVM, composição do capital em 2026-06-30, sem tesouraria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>Preço da ação (R$)</t>
-        </is>
-      </c>
-      <c r="D59" s="23" t="n">
-        <v>67.64</v>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>B3, fechamento de 2026-10-08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Valor de mercado (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="n">
-        <v>275454.8362</v>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
           <t>Ações em circulação pelo preço de cada classe.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="4">
     <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>$L$4:$L$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da faixa" error="Use um valor entre o pessimista e o otimista." type="decimal" operator="between">
+      <formula1>=MIN($E$8:$G$8)</formula1>
+      <formula2>=MAX($E$8:$G$8)</formula2>
+    </dataValidation>
+    <dataValidation sqref="H9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da faixa" error="Use um valor entre o pessimista e o otimista." type="decimal" operator="between">
+      <formula1>=MIN($E$9:$G$9)</formula1>
+      <formula2>=MAX($E$9:$G$9)</formula2>
+    </dataValidation>
+    <dataValidation sqref="H10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fora da faixa" error="Use um valor entre o pessimista e o otimista." type="decimal" operator="between">
+      <formula1>=MIN($E$10:$G$10)</formula1>
+      <formula2>=MAX($E$10:$G$10)</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2126,7 +1781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:K67"/>
+  <dimension ref="B1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2210,20 +1865,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Demonstração do resultado</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
+      <c r="I5" s="27" t="n"/>
+      <c r="J5" s="27" t="n"/>
+      <c r="K5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
@@ -2398,2119 +2053,2239 @@
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Total de despesas/receitas operacionais</t>
+          <t>Perdas por recuperabilidade de ativos (impairment)</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>-10106.478</v>
+        <v>-3523.458</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>-62564.583</v>
+        <v>-20762.371</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>-57893.647</v>
+        <v>-11818.792</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-34922</v>
+        <v>-2352</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>-11987</v>
+        <v>3833</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>-22778</v>
+        <v>-1317</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>-19228</v>
+        <v>510</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>-42739</v>
+        <v>-25147</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>-42048</v>
+        <v>-23490</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Equivalência patrimonial</t>
+          <t>Total de despesas/receitas operacionais</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>-693.486</v>
+        <v>-10106.478</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>-2683.903</v>
+        <v>-62564.583</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>-5435.93</v>
+        <v>-57893.647</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>-6947</v>
+        <v>-34922</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1616</v>
+        <v>-11987</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>-5434</v>
+        <v>-22778</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-1570</v>
+        <v>-19228</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>-1170</v>
+        <v>-42739</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>-453</v>
+        <v>-42048</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>EBIT (resultado antes do financeiro e dos tributos)</t>
+          <t>Equivalência patrimonial</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>43175.744</v>
+        <v>-693.486</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>2239.775</v>
+        <v>-2683.903</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>52067.618</v>
+        <v>-5435.93</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>141335</v>
+        <v>-6947</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>90326</v>
+        <v>1616</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>65272</v>
+        <v>-5434</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>55459</v>
+        <v>-1570</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>31969</v>
+        <v>-1170</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>34110</v>
+        <v>-453</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Resultado financeiro</t>
+          <t>EBIT (resultado antes do financeiro e dos tributos)</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>-18057.519</v>
+        <v>43175.744</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>-13444.786</v>
+        <v>2239.775</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>-24140.63</v>
+        <v>52067.618</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>17812</v>
+        <v>141335</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>11378</v>
+        <v>90326</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>-9718</v>
+        <v>65272</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-21235</v>
+        <v>55459</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>-5276</v>
+        <v>31969</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>-9699</v>
+        <v>34110</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Lucro antes dos tributos</t>
+          <t>Resultado financeiro</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>25118.225</v>
+        <v>-18057.519</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>-11205.011</v>
+        <v>-13444.786</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>27926.988</v>
+        <v>-24140.63</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>159147</v>
+        <v>17812</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>101704</v>
+        <v>11378</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>55554</v>
+        <v>-9718</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>34224</v>
+        <v>-21235</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>26693</v>
+        <v>-5276</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>24411</v>
+        <v>-9699</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Imposto de renda e CSLL</t>
+          <t>Lucro antes dos tributos</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>965.98</v>
+        <v>25118.225</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>2508.971</v>
+        <v>-11205.011</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>-3024.647</v>
+        <v>27926.988</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>-25320</v>
+        <v>159147</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>-15185</v>
+        <v>101704</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>-15000</v>
+        <v>55554</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-3793</v>
+        <v>34224</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>-14882</v>
+        <v>26693</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>-15720</v>
+        <v>24411</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Lucro líquido consolidado</t>
+          <t>Imposto de renda e CSLL</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>25773.768</v>
+        <v>965.98</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>-8696.040000000001</v>
+        <v>2508.971</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>24902.341</v>
+        <v>-3024.647</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>121343</v>
+        <v>-25320</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>96337</v>
+        <v>-15185</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>40554</v>
+        <v>-15000</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>30431</v>
+        <v>-3793</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>11811</v>
+        <v>-14882</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>8691</v>
+        <v>-15720</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Lucro líquido consolidado</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>25773.768</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>-8696.040000000001</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>24902.341</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>121343</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>96337</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>40554</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>30431</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>11811</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>8691</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
           <t>Lucro atribuído aos controladores</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C19" s="12" t="n">
         <v>25656.526</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>-6671.445</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>26712.713</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>121228</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>95924</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>39940</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>31592</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>13814</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>10369</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="24" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Fluxo de caixa</t>
         </is>
       </c>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="25" t="n"/>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="25" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Depreciação, amortização e exaustão</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>12238.935</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>14750.733</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>16679.216</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>16379</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>16386</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>15300</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>16525</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>17306</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>17823</v>
-      </c>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+      <c r="I20" s="27" t="n"/>
+      <c r="J20" s="27" t="n"/>
+      <c r="K20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Caixa das atividades operacionais</t>
+          <t>Depreciação, amortização e exaustão</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>47930.771</v>
+        <v>12238.935</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>47283.755</v>
+        <v>14750.733</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>75207.87300000001</v>
+        <v>16679.216</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>136766</v>
+        <v>16379</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>58201</v>
+        <v>16386</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>65905</v>
+        <v>15300</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50199</v>
+        <v>16525</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>48765</v>
+        <v>17306</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>50599</v>
+        <v>17823</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Investimento em imobilizado e intangível (capex)</t>
+          <t>Caixa das atividades operacionais</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>13978.533</v>
+        <v>47930.771</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>14773.97</v>
+        <v>47283.755</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>22725.636</v>
+        <v>75207.87300000001</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>27301</v>
+        <v>136766</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>28184</v>
+        <v>58201</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>29446</v>
+        <v>65905</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>35098</v>
+        <v>50199</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33390</v>
+        <v>48765</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>31848</v>
+        <v>50599</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>Investimento em imobilizado e intangível (capex)</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>13978.533</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>14773.97</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>22725.636</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>27301</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>28184</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>29446</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>35098</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>33390</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>31848</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
           <t>Dividendos e JCP pagos</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C24" s="12" t="n">
         <v>13050.573</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D24" s="12" t="n">
         <v>695.071</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>18708.953</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>73287</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>34157</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>27967</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>20663</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>19971</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>23071</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="24" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Balanço patrimonial</t>
         </is>
       </c>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Caixa e equivalentes</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>22412.547</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>29627.092</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>70085.56600000001</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>65409</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>24711</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>17474</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>30671</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>40563</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>28871</v>
-      </c>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="27" t="n"/>
+      <c r="I25" s="27" t="n"/>
+      <c r="J25" s="27" t="n"/>
+      <c r="K25" s="27" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Aplicações financeiras</t>
+          <t>Caixa e equivalentes</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>0</v>
+        <v>22412.547</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0</v>
+        <v>29627.092</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0</v>
+        <v>70085.56600000001</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1028</v>
+        <v>65409</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>320</v>
+        <v>24711</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>250</v>
+        <v>17474</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>331</v>
+        <v>30671</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>1066</v>
+        <v>40563</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>971</v>
+        <v>28871</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Contas a receber</t>
+          <t>Aplicações financeiras</t>
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>11669.973</v>
+        <v>0</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>11483.278</v>
+        <v>0</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>27233.885</v>
+        <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>21840</v>
+        <v>1028</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>22537</v>
+        <v>320</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>20317</v>
+        <v>250</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>14600</v>
+        <v>331</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>12639</v>
+        <v>1066</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13534</v>
+        <v>971</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Estoques</t>
+          <t>Contas a receber</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>17215.947</v>
+        <v>11669.973</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>17228.428</v>
+        <v>11483.278</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>21102.768</v>
+        <v>27233.885</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>24429</v>
+        <v>21840</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>23386</v>
+        <v>22537</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>22679</v>
+        <v>20317</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28513</v>
+        <v>14600</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32666</v>
+        <v>12639</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>32424</v>
+        <v>13534</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Ativo circulante</t>
+          <t>Estoques</t>
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>59256.115</v>
+        <v>17215.947</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>68697.54700000001</v>
+        <v>17228.428</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>126805.173</v>
+        <v>21102.768</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>124800</v>
+        <v>24429</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>81009</v>
+        <v>23386</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>90529</v>
+        <v>22679</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>83476</v>
+        <v>28513</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>100645</v>
+        <v>32666</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>91411</v>
+        <v>32424</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Investimentos em coligadas</t>
+          <t>Ativo circulante</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>12495.002</v>
+        <v>59256.115</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>11277.871</v>
+        <v>68697.54700000001</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>10556.64</v>
+        <v>126805.173</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>9771</v>
+        <v>124800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>9381</v>
+        <v>81009</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9061</v>
+        <v>90529</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>28158</v>
+        <v>83476</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27674</v>
+        <v>100645</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>27248</v>
+        <v>91411</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Imobilizado</t>
+          <t>Investimentos em coligadas</t>
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>187481.499</v>
+        <v>12495.002</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>187733.155</v>
+        <v>11277.871</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>213835.752</v>
+        <v>10556.64</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>233995</v>
+        <v>9771</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>234472</v>
+        <v>9381</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>234302</v>
+        <v>9061</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>247594</v>
+        <v>28158</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>240040</v>
+        <v>27674</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>240188</v>
+        <v>27248</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Intangível</t>
+          <t>Imobilizado</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>30850.392</v>
+        <v>187481.499</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>34256.976</v>
+        <v>187733.155</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>48308.512</v>
+        <v>213835.752</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>50287</v>
+        <v>233995</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>53421</v>
+        <v>234472</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>56309</v>
+        <v>234302</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>65105</v>
+        <v>247594</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>49261</v>
+        <v>240040</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>48775</v>
+        <v>240188</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Ativo total</t>
+          <t>Intangível</t>
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>341714.838</v>
+        <v>30850.392</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>369670.328</v>
+        <v>34256.976</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>478129.515</v>
+        <v>48308.512</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>499128</v>
+        <v>50287</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>453387</v>
+        <v>53421</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>455984</v>
+        <v>56309</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>496325</v>
+        <v>65105</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>476094</v>
+        <v>49261</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>462161</v>
+        <v>48775</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Fornecedores</t>
+          <t>Ativo total</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>13609.716</v>
+        <v>341714.838</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>16555.739</v>
+        <v>369670.328</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>17495.96</v>
+        <v>478129.515</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>19393</v>
+        <v>499128</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>23278</v>
+        <v>453387</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>25523</v>
+        <v>455984</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>26217</v>
+        <v>496325</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>30621</v>
+        <v>476094</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>32113</v>
+        <v>462161</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Empréstimos e financiamentos - curto prazo</t>
+          <t>Fornecedores</t>
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>3888.522</v>
+        <v>13609.716</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>5804.801</v>
+        <v>16555.739</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>5901.375</v>
+        <v>17495.96</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>6720</v>
+        <v>19393</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2552</v>
+        <v>23278</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>4940</v>
+        <v>25523</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>7223</v>
+        <v>26217</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>3731</v>
+        <v>30621</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>6534</v>
+        <v>32113</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Passivo circulante</t>
+          <t>Empréstimos e financiamentos - curto prazo</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>35516.662</v>
+        <v>3888.522</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>55805.644</v>
+        <v>5804.801</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>75837.515</v>
+        <v>5901.375</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>84814</v>
+        <v>6720</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>72478</v>
+        <v>2552</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>70948</v>
+        <v>4940</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>81055</v>
+        <v>7223</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>87320</v>
+        <v>3731</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>76703</v>
+        <v>6534</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Empréstimos e financiamentos - longo prazo</t>
+          <t>Passivo circulante</t>
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>56039.432</v>
+        <v>35516.662</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>54037.929</v>
+        <v>55805.644</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>72187.72</v>
+        <v>75837.515</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>70189</v>
+        <v>84814</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>63778</v>
+        <v>72478</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>62464</v>
+        <v>70948</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>88789</v>
+        <v>81055</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>99726</v>
+        <v>87320</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>91500</v>
+        <v>76703</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Patrimônio líquido consolidado</t>
+          <t>Empréstimos e financiamentos - longo prazo</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>173682.178</v>
+        <v>56039.432</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>157149.353</v>
+        <v>54037.929</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>180985.984</v>
+        <v>72187.72</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>197058</v>
+        <v>70189</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>194894</v>
+        <v>63778</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>198325</v>
+        <v>62464</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>213720</v>
+        <v>88789</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>188926</v>
+        <v>99726</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>201467</v>
+        <v>91500</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>Patrimônio líquido consolidado</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>173682.178</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>157149.353</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>180985.984</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>197058</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>194894</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>198325</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>213720</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>188926</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>201467</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Participação de não controladores</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C40" s="12" t="n">
         <v>3279.552</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D40" s="12" t="n">
         <v>-4330.947</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E40" s="12" t="n">
         <v>-4798.995</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>4655</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>7782</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>7360</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>6948</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>4627</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>4832</v>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="24" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Indicadores (fórmulas)</t>
         </is>
       </c>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="25" t="n"/>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="25" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA (EBIT + depreciação)</t>
-        </is>
-      </c>
-      <c r="C41" s="12">
-        <f>C13+C20</f>
-        <v/>
-      </c>
-      <c r="D41" s="12">
-        <f>D13+D20</f>
-        <v/>
-      </c>
-      <c r="E41" s="12">
-        <f>E13+E20</f>
-        <v/>
-      </c>
-      <c r="F41" s="12">
-        <f>F13+F20</f>
-        <v/>
-      </c>
-      <c r="G41" s="12">
-        <f>G13+G20</f>
-        <v/>
-      </c>
-      <c r="H41" s="12">
-        <f>H13+H20</f>
-        <v/>
-      </c>
-      <c r="I41" s="12">
-        <f>I13+I20</f>
-        <v/>
-      </c>
-      <c r="J41" s="12">
-        <f>J13+J20</f>
-        <v/>
-      </c>
-      <c r="K41" s="12">
-        <f>K13+K20</f>
-        <v/>
-      </c>
+      <c r="C41" s="27" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="27" t="n"/>
+      <c r="I41" s="27" t="n"/>
+      <c r="J41" s="27" t="n"/>
+      <c r="K41" s="27" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Custo caixa (custo sem depreciação)</t>
+          <t>EBITDA (EBIT + depreciação)</t>
         </is>
       </c>
       <c r="C42" s="12">
-        <f>C7+C20</f>
+        <f>C14+C21</f>
         <v/>
       </c>
       <c r="D42" s="12">
-        <f>D7+D20</f>
+        <f>D14+D21</f>
         <v/>
       </c>
       <c r="E42" s="12">
-        <f>E7+E20</f>
+        <f>E14+E21</f>
         <v/>
       </c>
       <c r="F42" s="12">
-        <f>F7+F20</f>
+        <f>F14+F21</f>
         <v/>
       </c>
       <c r="G42" s="12">
-        <f>G7+G20</f>
+        <f>G14+G21</f>
         <v/>
       </c>
       <c r="H42" s="12">
-        <f>H7+H20</f>
+        <f>H14+H21</f>
         <v/>
       </c>
       <c r="I42" s="12">
-        <f>I7+I20</f>
+        <f>I14+I21</f>
         <v/>
       </c>
       <c r="J42" s="12">
-        <f>J7+J20</f>
+        <f>J14+J21</f>
         <v/>
       </c>
       <c r="K42" s="12">
-        <f>K7+K20</f>
+        <f>K14+K21</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Outras receitas/despesas operacionais</t>
+          <t>EBITDA sem perdas por recuperabilidade</t>
         </is>
       </c>
       <c r="C43" s="12">
-        <f>C11-C9-C10-C12</f>
+        <f>C42-C11</f>
         <v/>
       </c>
       <c r="D43" s="12">
-        <f>D11-D9-D10-D12</f>
+        <f>D42-D11</f>
         <v/>
       </c>
       <c r="E43" s="12">
-        <f>E11-E9-E10-E12</f>
+        <f>E42-E11</f>
         <v/>
       </c>
       <c r="F43" s="12">
-        <f>F11-F9-F10-F12</f>
+        <f>F42-F11</f>
         <v/>
       </c>
       <c r="G43" s="12">
-        <f>G11-G9-G10-G12</f>
+        <f>G42-G11</f>
         <v/>
       </c>
       <c r="H43" s="12">
-        <f>H11-H9-H10-H12</f>
+        <f>H42-H11</f>
         <v/>
       </c>
       <c r="I43" s="12">
-        <f>I11-I9-I10-I12</f>
+        <f>I42-I11</f>
         <v/>
       </c>
       <c r="J43" s="12">
-        <f>J11-J9-J10-J12</f>
+        <f>J42-J11</f>
         <v/>
       </c>
       <c r="K43" s="12">
-        <f>K11-K9-K10-K12</f>
+        <f>K42-K11</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>NOPAT (lucro operacional após imposto)</t>
-        </is>
-      </c>
-      <c r="C44" s="12">
-        <f>(C13-C12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="D44" s="12">
-        <f>(D13-D12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="E44" s="12">
-        <f>(E13-E12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="F44" s="12">
-        <f>(F13-F12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="G44" s="12">
-        <f>(G13-G12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="H44" s="12">
-        <f>(H13-H12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="I44" s="12">
-        <f>(I13-I12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="J44" s="12">
-        <f>(J13-J12)*(1-'Premissas'!$D$42)</f>
-        <v/>
-      </c>
-      <c r="K44" s="12">
-        <f>(K13-K12)*(1-'Premissas'!$D$42)</f>
+          <t>Margem EBITDA sem perdas por recuperabilidade</t>
+        </is>
+      </c>
+      <c r="C44" s="11">
+        <f>C43/C6</f>
+        <v/>
+      </c>
+      <c r="D44" s="11">
+        <f>D43/D6</f>
+        <v/>
+      </c>
+      <c r="E44" s="11">
+        <f>E43/E6</f>
+        <v/>
+      </c>
+      <c r="F44" s="11">
+        <f>F43/F6</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>G43/G6</f>
+        <v/>
+      </c>
+      <c r="H44" s="11">
+        <f>H43/H6</f>
+        <v/>
+      </c>
+      <c r="I44" s="11">
+        <f>I43/I6</f>
+        <v/>
+      </c>
+      <c r="J44" s="11">
+        <f>J43/J6</f>
+        <v/>
+      </c>
+      <c r="K44" s="11">
+        <f>K43/K6</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Crescimento da receita</t>
-        </is>
-      </c>
-      <c r="D45" s="11">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E45" s="11">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F45" s="11">
-        <f>F6/E6-1</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>G6/F6-1</f>
-        <v/>
-      </c>
-      <c r="H45" s="11">
-        <f>H6/G6-1</f>
-        <v/>
-      </c>
-      <c r="I45" s="11">
-        <f>I6/H6-1</f>
-        <v/>
-      </c>
-      <c r="J45" s="11">
-        <f>J6/I6-1</f>
-        <v/>
-      </c>
-      <c r="K45" s="11">
-        <f>K6/J6-1</f>
+          <t>Custo caixa (custo sem depreciação)</t>
+        </is>
+      </c>
+      <c r="C45" s="12">
+        <f>C7+C21</f>
+        <v/>
+      </c>
+      <c r="D45" s="12">
+        <f>D7+D21</f>
+        <v/>
+      </c>
+      <c r="E45" s="12">
+        <f>E7+E21</f>
+        <v/>
+      </c>
+      <c r="F45" s="12">
+        <f>F7+F21</f>
+        <v/>
+      </c>
+      <c r="G45" s="12">
+        <f>G7+G21</f>
+        <v/>
+      </c>
+      <c r="H45" s="12">
+        <f>H7+H21</f>
+        <v/>
+      </c>
+      <c r="I45" s="12">
+        <f>I7+I21</f>
+        <v/>
+      </c>
+      <c r="J45" s="12">
+        <f>J7+J21</f>
+        <v/>
+      </c>
+      <c r="K45" s="12">
+        <f>K7+K21</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Margem bruta</t>
-        </is>
-      </c>
-      <c r="C46" s="11">
-        <f>C8/C6</f>
-        <v/>
-      </c>
-      <c r="D46" s="11">
-        <f>D8/D6</f>
-        <v/>
-      </c>
-      <c r="E46" s="11">
-        <f>E8/E6</f>
-        <v/>
-      </c>
-      <c r="F46" s="11">
-        <f>F8/F6</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>G8/G6</f>
-        <v/>
-      </c>
-      <c r="H46" s="11">
-        <f>H8/H6</f>
-        <v/>
-      </c>
-      <c r="I46" s="11">
-        <f>I8/I6</f>
-        <v/>
-      </c>
-      <c r="J46" s="11">
-        <f>J8/J6</f>
-        <v/>
-      </c>
-      <c r="K46" s="11">
-        <f>K8/K6</f>
+          <t>Outras receitas/despesas operacionais</t>
+        </is>
+      </c>
+      <c r="C46" s="12">
+        <f>C12-C9-C10-C13</f>
+        <v/>
+      </c>
+      <c r="D46" s="12">
+        <f>D12-D9-D10-D13</f>
+        <v/>
+      </c>
+      <c r="E46" s="12">
+        <f>E12-E9-E10-E13</f>
+        <v/>
+      </c>
+      <c r="F46" s="12">
+        <f>F12-F9-F10-F13</f>
+        <v/>
+      </c>
+      <c r="G46" s="12">
+        <f>G12-G9-G10-G13</f>
+        <v/>
+      </c>
+      <c r="H46" s="12">
+        <f>H12-H9-H10-H13</f>
+        <v/>
+      </c>
+      <c r="I46" s="12">
+        <f>I12-I9-I10-I13</f>
+        <v/>
+      </c>
+      <c r="J46" s="12">
+        <f>J12-J9-J10-J13</f>
+        <v/>
+      </c>
+      <c r="K46" s="12">
+        <f>K12-K9-K10-K13</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Margem EBITDA</t>
-        </is>
-      </c>
-      <c r="C47" s="11">
-        <f>C41/C6</f>
-        <v/>
-      </c>
-      <c r="D47" s="11">
-        <f>D41/D6</f>
-        <v/>
-      </c>
-      <c r="E47" s="11">
-        <f>E41/E6</f>
-        <v/>
-      </c>
-      <c r="F47" s="11">
-        <f>F41/F6</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>G41/G6</f>
-        <v/>
-      </c>
-      <c r="H47" s="11">
-        <f>H41/H6</f>
-        <v/>
-      </c>
-      <c r="I47" s="11">
-        <f>I41/I6</f>
-        <v/>
-      </c>
-      <c r="J47" s="11">
-        <f>J41/J6</f>
-        <v/>
-      </c>
-      <c r="K47" s="11">
-        <f>K41/K6</f>
+          <t>NOPAT (lucro operacional após imposto de 34%)</t>
+        </is>
+      </c>
+      <c r="C47" s="12">
+        <f>(C14-C13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="D47" s="12">
+        <f>(D14-D13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="E47" s="12">
+        <f>(E14-E13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="F47" s="12">
+        <f>(F14-F13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="G47" s="12">
+        <f>(G14-G13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="H47" s="12">
+        <f>(H14-H13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="I47" s="12">
+        <f>(I14-I13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="J47" s="12">
+        <f>(J14-J13)*(1-0.34)</f>
+        <v/>
+      </c>
+      <c r="K47" s="12">
+        <f>(K14-K13)*(1-0.34)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Margem EBIT</t>
-        </is>
-      </c>
-      <c r="C48" s="11">
-        <f>C13/C6</f>
-        <v/>
+          <t>Crescimento da receita</t>
+        </is>
       </c>
       <c r="D48" s="11">
-        <f>D13/D6</f>
+        <f>D6/C6-1</f>
         <v/>
       </c>
       <c r="E48" s="11">
-        <f>E13/E6</f>
+        <f>E6/D6-1</f>
         <v/>
       </c>
       <c r="F48" s="11">
-        <f>F13/F6</f>
+        <f>F6/E6-1</f>
         <v/>
       </c>
       <c r="G48" s="11">
-        <f>G13/G6</f>
+        <f>G6/F6-1</f>
         <v/>
       </c>
       <c r="H48" s="11">
-        <f>H13/H6</f>
+        <f>H6/G6-1</f>
         <v/>
       </c>
       <c r="I48" s="11">
-        <f>I13/I6</f>
+        <f>I6/H6-1</f>
         <v/>
       </c>
       <c r="J48" s="11">
-        <f>J13/J6</f>
+        <f>J6/I6-1</f>
         <v/>
       </c>
       <c r="K48" s="11">
-        <f>K13/K6</f>
+        <f>K6/J6-1</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Margem líquida</t>
+          <t>Margem bruta</t>
         </is>
       </c>
       <c r="C49" s="11">
-        <f>C17/C6</f>
+        <f>C8/C6</f>
         <v/>
       </c>
       <c r="D49" s="11">
-        <f>D17/D6</f>
+        <f>D8/D6</f>
         <v/>
       </c>
       <c r="E49" s="11">
-        <f>E17/E6</f>
+        <f>E8/E6</f>
         <v/>
       </c>
       <c r="F49" s="11">
-        <f>F17/F6</f>
+        <f>F8/F6</f>
         <v/>
       </c>
       <c r="G49" s="11">
-        <f>G17/G6</f>
+        <f>G8/G6</f>
         <v/>
       </c>
       <c r="H49" s="11">
-        <f>H17/H6</f>
+        <f>H8/H6</f>
         <v/>
       </c>
       <c r="I49" s="11">
-        <f>I17/I6</f>
+        <f>I8/I6</f>
         <v/>
       </c>
       <c r="J49" s="11">
-        <f>J17/J6</f>
+        <f>J8/J6</f>
         <v/>
       </c>
       <c r="K49" s="11">
-        <f>K17/K6</f>
+        <f>K8/K6</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Outras operacionais / receita</t>
+          <t>Margem EBITDA</t>
         </is>
       </c>
       <c r="C50" s="11">
-        <f>C43/C6</f>
+        <f>C42/C6</f>
         <v/>
       </c>
       <c r="D50" s="11">
-        <f>D43/D6</f>
+        <f>D42/D6</f>
         <v/>
       </c>
       <c r="E50" s="11">
-        <f>E43/E6</f>
+        <f>E42/E6</f>
         <v/>
       </c>
       <c r="F50" s="11">
-        <f>F43/F6</f>
+        <f>F42/F6</f>
         <v/>
       </c>
       <c r="G50" s="11">
-        <f>G43/G6</f>
+        <f>G42/G6</f>
         <v/>
       </c>
       <c r="H50" s="11">
-        <f>H43/H6</f>
+        <f>H42/H6</f>
         <v/>
       </c>
       <c r="I50" s="11">
-        <f>I43/I6</f>
+        <f>I42/I6</f>
         <v/>
       </c>
       <c r="J50" s="11">
-        <f>J43/J6</f>
+        <f>J42/J6</f>
         <v/>
       </c>
       <c r="K50" s="11">
-        <f>K43/K6</f>
+        <f>K42/K6</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Capex / receita</t>
+          <t>Margem EBIT</t>
         </is>
       </c>
       <c r="C51" s="11">
-        <f>C22/C6</f>
+        <f>C14/C6</f>
         <v/>
       </c>
       <c r="D51" s="11">
-        <f>D22/D6</f>
+        <f>D14/D6</f>
         <v/>
       </c>
       <c r="E51" s="11">
-        <f>E22/E6</f>
+        <f>E14/E6</f>
         <v/>
       </c>
       <c r="F51" s="11">
-        <f>F22/F6</f>
+        <f>F14/F6</f>
         <v/>
       </c>
       <c r="G51" s="11">
-        <f>G22/G6</f>
+        <f>G14/G6</f>
         <v/>
       </c>
       <c r="H51" s="11">
-        <f>H22/H6</f>
+        <f>H14/H6</f>
         <v/>
       </c>
       <c r="I51" s="11">
-        <f>I22/I6</f>
+        <f>I14/I6</f>
         <v/>
       </c>
       <c r="J51" s="11">
-        <f>J22/J6</f>
+        <f>J14/J6</f>
         <v/>
       </c>
       <c r="K51" s="11">
-        <f>K22/K6</f>
+        <f>K14/K6</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Ativo fixo (imobilizado + intangível)</t>
-        </is>
-      </c>
-      <c r="C52" s="12">
-        <f>C31+C32</f>
-        <v/>
-      </c>
-      <c r="D52" s="12">
-        <f>D31+D32</f>
-        <v/>
-      </c>
-      <c r="E52" s="12">
-        <f>E31+E32</f>
-        <v/>
-      </c>
-      <c r="F52" s="12">
-        <f>F31+F32</f>
-        <v/>
-      </c>
-      <c r="G52" s="12">
-        <f>G31+G32</f>
-        <v/>
-      </c>
-      <c r="H52" s="12">
-        <f>H31+H32</f>
-        <v/>
-      </c>
-      <c r="I52" s="12">
-        <f>I31+I32</f>
-        <v/>
-      </c>
-      <c r="J52" s="12">
-        <f>J31+J32</f>
-        <v/>
-      </c>
-      <c r="K52" s="12">
-        <f>K31+K32</f>
+          <t>Margem líquida</t>
+        </is>
+      </c>
+      <c r="C52" s="11">
+        <f>C18/C6</f>
+        <v/>
+      </c>
+      <c r="D52" s="11">
+        <f>D18/D6</f>
+        <v/>
+      </c>
+      <c r="E52" s="11">
+        <f>E18/E6</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>F18/F6</f>
+        <v/>
+      </c>
+      <c r="G52" s="11">
+        <f>G18/G6</f>
+        <v/>
+      </c>
+      <c r="H52" s="11">
+        <f>H18/H6</f>
+        <v/>
+      </c>
+      <c r="I52" s="11">
+        <f>I18/I6</f>
+        <v/>
+      </c>
+      <c r="J52" s="11">
+        <f>J18/J6</f>
+        <v/>
+      </c>
+      <c r="K52" s="11">
+        <f>K18/K6</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Depreciação / ativo fixo do ano anterior</t>
-        </is>
+          <t>Outras operacionais / receita</t>
+        </is>
+      </c>
+      <c r="C53" s="11">
+        <f>C46/C6</f>
+        <v/>
       </c>
       <c r="D53" s="11">
-        <f>D20/C52</f>
+        <f>D46/D6</f>
         <v/>
       </c>
       <c r="E53" s="11">
-        <f>E20/D52</f>
+        <f>E46/E6</f>
         <v/>
       </c>
       <c r="F53" s="11">
-        <f>F20/E52</f>
+        <f>F46/F6</f>
         <v/>
       </c>
       <c r="G53" s="11">
-        <f>G20/F52</f>
+        <f>G46/G6</f>
         <v/>
       </c>
       <c r="H53" s="11">
-        <f>H20/G52</f>
+        <f>H46/H6</f>
         <v/>
       </c>
       <c r="I53" s="11">
-        <f>I20/H52</f>
+        <f>I46/I6</f>
         <v/>
       </c>
       <c r="J53" s="11">
-        <f>J20/I52</f>
+        <f>J46/J6</f>
         <v/>
       </c>
       <c r="K53" s="11">
-        <f>K20/J52</f>
+        <f>K46/K6</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Alíquota efetiva de imposto</t>
+          <t>Capex / receita</t>
         </is>
       </c>
       <c r="C54" s="11">
-        <f>-C16/C15</f>
+        <f>C23/C6</f>
         <v/>
       </c>
       <c r="D54" s="11">
-        <f>-D16/D15</f>
+        <f>D23/D6</f>
         <v/>
       </c>
       <c r="E54" s="11">
-        <f>-E16/E15</f>
+        <f>E23/E6</f>
         <v/>
       </c>
       <c r="F54" s="11">
-        <f>-F16/F15</f>
+        <f>F23/F6</f>
         <v/>
       </c>
       <c r="G54" s="11">
-        <f>-G16/G15</f>
+        <f>G23/G6</f>
         <v/>
       </c>
       <c r="H54" s="11">
-        <f>-H16/H15</f>
+        <f>H23/H6</f>
         <v/>
       </c>
       <c r="I54" s="11">
-        <f>-I16/I15</f>
+        <f>I23/I6</f>
         <v/>
       </c>
       <c r="J54" s="11">
-        <f>-J16/J15</f>
+        <f>J23/J6</f>
         <v/>
       </c>
       <c r="K54" s="11">
-        <f>-K16/K15</f>
+        <f>K23/K6</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de recebimento (dias)</t>
-        </is>
-      </c>
-      <c r="C55" s="17">
-        <f>C27/C6*365</f>
-        <v/>
-      </c>
-      <c r="D55" s="17">
-        <f>D27/D6*365</f>
-        <v/>
-      </c>
-      <c r="E55" s="17">
-        <f>E27/E6*365</f>
-        <v/>
-      </c>
-      <c r="F55" s="17">
-        <f>F27/F6*365</f>
-        <v/>
-      </c>
-      <c r="G55" s="17">
-        <f>G27/G6*365</f>
-        <v/>
-      </c>
-      <c r="H55" s="17">
-        <f>H27/H6*365</f>
-        <v/>
-      </c>
-      <c r="I55" s="17">
-        <f>I27/I6*365</f>
-        <v/>
-      </c>
-      <c r="J55" s="17">
-        <f>J27/J6*365</f>
-        <v/>
-      </c>
-      <c r="K55" s="17">
-        <f>K27/K6*365</f>
+          <t>Ativo fixo (imobilizado + intangível)</t>
+        </is>
+      </c>
+      <c r="C55" s="12">
+        <f>C32+C33</f>
+        <v/>
+      </c>
+      <c r="D55" s="12">
+        <f>D32+D33</f>
+        <v/>
+      </c>
+      <c r="E55" s="12">
+        <f>E32+E33</f>
+        <v/>
+      </c>
+      <c r="F55" s="12">
+        <f>F32+F33</f>
+        <v/>
+      </c>
+      <c r="G55" s="12">
+        <f>G32+G33</f>
+        <v/>
+      </c>
+      <c r="H55" s="12">
+        <f>H32+H33</f>
+        <v/>
+      </c>
+      <c r="I55" s="12">
+        <f>I32+I33</f>
+        <v/>
+      </c>
+      <c r="J55" s="12">
+        <f>J32+J33</f>
+        <v/>
+      </c>
+      <c r="K55" s="12">
+        <f>K32+K33</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de estoque (dias)</t>
-        </is>
-      </c>
-      <c r="C56" s="17">
-        <f>C28/-C42*365</f>
-        <v/>
-      </c>
-      <c r="D56" s="17">
-        <f>D28/-D42*365</f>
-        <v/>
-      </c>
-      <c r="E56" s="17">
-        <f>E28/-E42*365</f>
-        <v/>
-      </c>
-      <c r="F56" s="17">
-        <f>F28/-F42*365</f>
-        <v/>
-      </c>
-      <c r="G56" s="17">
-        <f>G28/-G42*365</f>
-        <v/>
-      </c>
-      <c r="H56" s="17">
-        <f>H28/-H42*365</f>
-        <v/>
-      </c>
-      <c r="I56" s="17">
-        <f>I28/-I42*365</f>
-        <v/>
-      </c>
-      <c r="J56" s="17">
-        <f>J28/-J42*365</f>
-        <v/>
-      </c>
-      <c r="K56" s="17">
-        <f>K28/-K42*365</f>
+          <t>Depreciação / ativo fixo do ano anterior</t>
+        </is>
+      </c>
+      <c r="D56" s="11">
+        <f>D21/C55</f>
+        <v/>
+      </c>
+      <c r="E56" s="11">
+        <f>E21/D55</f>
+        <v/>
+      </c>
+      <c r="F56" s="11">
+        <f>F21/E55</f>
+        <v/>
+      </c>
+      <c r="G56" s="11">
+        <f>G21/F55</f>
+        <v/>
+      </c>
+      <c r="H56" s="11">
+        <f>H21/G55</f>
+        <v/>
+      </c>
+      <c r="I56" s="11">
+        <f>I21/H55</f>
+        <v/>
+      </c>
+      <c r="J56" s="11">
+        <f>J21/I55</f>
+        <v/>
+      </c>
+      <c r="K56" s="11">
+        <f>K21/J55</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Prazo médio de pagamento (dias)</t>
-        </is>
-      </c>
-      <c r="C57" s="17">
-        <f>C34/-C42*365</f>
-        <v/>
-      </c>
-      <c r="D57" s="17">
-        <f>D34/-D42*365</f>
-        <v/>
-      </c>
-      <c r="E57" s="17">
-        <f>E34/-E42*365</f>
-        <v/>
-      </c>
-      <c r="F57" s="17">
-        <f>F34/-F42*365</f>
-        <v/>
-      </c>
-      <c r="G57" s="17">
-        <f>G34/-G42*365</f>
-        <v/>
-      </c>
-      <c r="H57" s="17">
-        <f>H34/-H42*365</f>
-        <v/>
-      </c>
-      <c r="I57" s="17">
-        <f>I34/-I42*365</f>
-        <v/>
-      </c>
-      <c r="J57" s="17">
-        <f>J34/-J42*365</f>
-        <v/>
-      </c>
-      <c r="K57" s="17">
-        <f>K34/-K42*365</f>
+          <t>Alíquota efetiva de imposto</t>
+        </is>
+      </c>
+      <c r="C57" s="11">
+        <f>-C17/C16</f>
+        <v/>
+      </c>
+      <c r="D57" s="11">
+        <f>-D17/D16</f>
+        <v/>
+      </c>
+      <c r="E57" s="11">
+        <f>-E17/E16</f>
+        <v/>
+      </c>
+      <c r="F57" s="11">
+        <f>-F17/F16</f>
+        <v/>
+      </c>
+      <c r="G57" s="11">
+        <f>-G17/G16</f>
+        <v/>
+      </c>
+      <c r="H57" s="11">
+        <f>-H17/H16</f>
+        <v/>
+      </c>
+      <c r="I57" s="11">
+        <f>-I17/I16</f>
+        <v/>
+      </c>
+      <c r="J57" s="11">
+        <f>-J17/J16</f>
+        <v/>
+      </c>
+      <c r="K57" s="11">
+        <f>-K17/K16</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Ciclo de caixa (dias)</t>
-        </is>
-      </c>
-      <c r="C58" s="17">
-        <f>C55+C56-C57</f>
-        <v/>
-      </c>
-      <c r="D58" s="17">
-        <f>D55+D56-D57</f>
-        <v/>
-      </c>
-      <c r="E58" s="17">
-        <f>E55+E56-E57</f>
-        <v/>
-      </c>
-      <c r="F58" s="17">
-        <f>F55+F56-F57</f>
-        <v/>
-      </c>
-      <c r="G58" s="17">
-        <f>G55+G56-G57</f>
-        <v/>
-      </c>
-      <c r="H58" s="17">
-        <f>H55+H56-H57</f>
-        <v/>
-      </c>
-      <c r="I58" s="17">
-        <f>I55+I56-I57</f>
-        <v/>
-      </c>
-      <c r="J58" s="17">
-        <f>J55+J56-J57</f>
-        <v/>
-      </c>
-      <c r="K58" s="17">
-        <f>K55+K56-K57</f>
+          <t>Prazo médio de recebimento (dias)</t>
+        </is>
+      </c>
+      <c r="C58" s="28">
+        <f>C28/C6*365</f>
+        <v/>
+      </c>
+      <c r="D58" s="28">
+        <f>D28/D6*365</f>
+        <v/>
+      </c>
+      <c r="E58" s="28">
+        <f>E28/E6*365</f>
+        <v/>
+      </c>
+      <c r="F58" s="28">
+        <f>F28/F6*365</f>
+        <v/>
+      </c>
+      <c r="G58" s="28">
+        <f>G28/G6*365</f>
+        <v/>
+      </c>
+      <c r="H58" s="28">
+        <f>H28/H6*365</f>
+        <v/>
+      </c>
+      <c r="I58" s="28">
+        <f>I28/I6*365</f>
+        <v/>
+      </c>
+      <c r="J58" s="28">
+        <f>J28/J6*365</f>
+        <v/>
+      </c>
+      <c r="K58" s="28">
+        <f>K28/K6*365</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Capital de giro (receber + estoques - fornecedores)</t>
-        </is>
-      </c>
-      <c r="C59" s="12">
-        <f>C27+C28-C34</f>
-        <v/>
-      </c>
-      <c r="D59" s="12">
-        <f>D27+D28-D34</f>
-        <v/>
-      </c>
-      <c r="E59" s="12">
-        <f>E27+E28-E34</f>
-        <v/>
-      </c>
-      <c r="F59" s="12">
-        <f>F27+F28-F34</f>
-        <v/>
-      </c>
-      <c r="G59" s="12">
-        <f>G27+G28-G34</f>
-        <v/>
-      </c>
-      <c r="H59" s="12">
-        <f>H27+H28-H34</f>
-        <v/>
-      </c>
-      <c r="I59" s="12">
-        <f>I27+I28-I34</f>
-        <v/>
-      </c>
-      <c r="J59" s="12">
-        <f>J27+J28-J34</f>
-        <v/>
-      </c>
-      <c r="K59" s="12">
-        <f>K27+K28-K34</f>
+          <t>Prazo médio de estoque (dias)</t>
+        </is>
+      </c>
+      <c r="C59" s="28">
+        <f>C29/-C45*365</f>
+        <v/>
+      </c>
+      <c r="D59" s="28">
+        <f>D29/-D45*365</f>
+        <v/>
+      </c>
+      <c r="E59" s="28">
+        <f>E29/-E45*365</f>
+        <v/>
+      </c>
+      <c r="F59" s="28">
+        <f>F29/-F45*365</f>
+        <v/>
+      </c>
+      <c r="G59" s="28">
+        <f>G29/-G45*365</f>
+        <v/>
+      </c>
+      <c r="H59" s="28">
+        <f>H29/-H45*365</f>
+        <v/>
+      </c>
+      <c r="I59" s="28">
+        <f>I29/-I45*365</f>
+        <v/>
+      </c>
+      <c r="J59" s="28">
+        <f>J29/-J45*365</f>
+        <v/>
+      </c>
+      <c r="K59" s="28">
+        <f>K29/-K45*365</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Caixa e aplicações</t>
-        </is>
-      </c>
-      <c r="C60" s="12">
-        <f>C25+C26</f>
-        <v/>
-      </c>
-      <c r="D60" s="12">
-        <f>D25+D26</f>
-        <v/>
-      </c>
-      <c r="E60" s="12">
-        <f>E25+E26</f>
-        <v/>
-      </c>
-      <c r="F60" s="12">
-        <f>F25+F26</f>
-        <v/>
-      </c>
-      <c r="G60" s="12">
-        <f>G25+G26</f>
-        <v/>
-      </c>
-      <c r="H60" s="12">
-        <f>H25+H26</f>
-        <v/>
-      </c>
-      <c r="I60" s="12">
-        <f>I25+I26</f>
-        <v/>
-      </c>
-      <c r="J60" s="12">
-        <f>J25+J26</f>
-        <v/>
-      </c>
-      <c r="K60" s="12">
-        <f>K25+K26</f>
+          <t>Prazo médio de pagamento (dias)</t>
+        </is>
+      </c>
+      <c r="C60" s="28">
+        <f>C35/-C45*365</f>
+        <v/>
+      </c>
+      <c r="D60" s="28">
+        <f>D35/-D45*365</f>
+        <v/>
+      </c>
+      <c r="E60" s="28">
+        <f>E35/-E45*365</f>
+        <v/>
+      </c>
+      <c r="F60" s="28">
+        <f>F35/-F45*365</f>
+        <v/>
+      </c>
+      <c r="G60" s="28">
+        <f>G35/-G45*365</f>
+        <v/>
+      </c>
+      <c r="H60" s="28">
+        <f>H35/-H45*365</f>
+        <v/>
+      </c>
+      <c r="I60" s="28">
+        <f>I35/-I45*365</f>
+        <v/>
+      </c>
+      <c r="J60" s="28">
+        <f>J35/-J45*365</f>
+        <v/>
+      </c>
+      <c r="K60" s="28">
+        <f>K35/-K45*365</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Dívida bruta</t>
-        </is>
-      </c>
-      <c r="C61" s="12">
-        <f>C35+C37</f>
-        <v/>
-      </c>
-      <c r="D61" s="12">
-        <f>D35+D37</f>
-        <v/>
-      </c>
-      <c r="E61" s="12">
-        <f>E35+E37</f>
-        <v/>
-      </c>
-      <c r="F61" s="12">
-        <f>F35+F37</f>
-        <v/>
-      </c>
-      <c r="G61" s="12">
-        <f>G35+G37</f>
-        <v/>
-      </c>
-      <c r="H61" s="12">
-        <f>H35+H37</f>
-        <v/>
-      </c>
-      <c r="I61" s="12">
-        <f>I35+I37</f>
-        <v/>
-      </c>
-      <c r="J61" s="12">
-        <f>J35+J37</f>
-        <v/>
-      </c>
-      <c r="K61" s="12">
-        <f>K35+K37</f>
+          <t>Ciclo de caixa (dias)</t>
+        </is>
+      </c>
+      <c r="C61" s="28">
+        <f>C58+C59-C60</f>
+        <v/>
+      </c>
+      <c r="D61" s="28">
+        <f>D58+D59-D60</f>
+        <v/>
+      </c>
+      <c r="E61" s="28">
+        <f>E58+E59-E60</f>
+        <v/>
+      </c>
+      <c r="F61" s="28">
+        <f>F58+F59-F60</f>
+        <v/>
+      </c>
+      <c r="G61" s="28">
+        <f>G58+G59-G60</f>
+        <v/>
+      </c>
+      <c r="H61" s="28">
+        <f>H58+H59-H60</f>
+        <v/>
+      </c>
+      <c r="I61" s="28">
+        <f>I58+I59-I60</f>
+        <v/>
+      </c>
+      <c r="J61" s="28">
+        <f>J58+J59-J60</f>
+        <v/>
+      </c>
+      <c r="K61" s="28">
+        <f>K58+K59-K60</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Dívida líquida</t>
+          <t>Capital de giro (receber + estoques - fornecedores)</t>
         </is>
       </c>
       <c r="C62" s="12">
-        <f>C61-C60</f>
+        <f>C28+C29-C35</f>
         <v/>
       </c>
       <c r="D62" s="12">
-        <f>D61-D60</f>
+        <f>D28+D29-D35</f>
         <v/>
       </c>
       <c r="E62" s="12">
-        <f>E61-E60</f>
+        <f>E28+E29-E35</f>
         <v/>
       </c>
       <c r="F62" s="12">
-        <f>F61-F60</f>
+        <f>F28+F29-F35</f>
         <v/>
       </c>
       <c r="G62" s="12">
-        <f>G61-G60</f>
+        <f>G28+G29-G35</f>
         <v/>
       </c>
       <c r="H62" s="12">
-        <f>H61-H60</f>
+        <f>H28+H29-H35</f>
         <v/>
       </c>
       <c r="I62" s="12">
-        <f>I61-I60</f>
+        <f>I28+I29-I35</f>
         <v/>
       </c>
       <c r="J62" s="12">
-        <f>J61-J60</f>
+        <f>J28+J29-J35</f>
         <v/>
       </c>
       <c r="K62" s="12">
-        <f>K61-K60</f>
+        <f>K28+K29-K35</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Dívida líquida / EBITDA</t>
-        </is>
-      </c>
-      <c r="C63" s="26">
-        <f>C62/C41</f>
-        <v/>
-      </c>
-      <c r="D63" s="26">
-        <f>D62/D41</f>
-        <v/>
-      </c>
-      <c r="E63" s="26">
-        <f>E62/E41</f>
-        <v/>
-      </c>
-      <c r="F63" s="26">
-        <f>F62/F41</f>
-        <v/>
-      </c>
-      <c r="G63" s="26">
-        <f>G62/G41</f>
-        <v/>
-      </c>
-      <c r="H63" s="26">
-        <f>H62/H41</f>
-        <v/>
-      </c>
-      <c r="I63" s="26">
-        <f>I62/I41</f>
-        <v/>
-      </c>
-      <c r="J63" s="26">
-        <f>J62/J41</f>
-        <v/>
-      </c>
-      <c r="K63" s="26">
-        <f>K62/K41</f>
+          <t>Caixa e aplicações</t>
+        </is>
+      </c>
+      <c r="C63" s="12">
+        <f>C26+C27</f>
+        <v/>
+      </c>
+      <c r="D63" s="12">
+        <f>D26+D27</f>
+        <v/>
+      </c>
+      <c r="E63" s="12">
+        <f>E26+E27</f>
+        <v/>
+      </c>
+      <c r="F63" s="12">
+        <f>F26+F27</f>
+        <v/>
+      </c>
+      <c r="G63" s="12">
+        <f>G26+G27</f>
+        <v/>
+      </c>
+      <c r="H63" s="12">
+        <f>H26+H27</f>
+        <v/>
+      </c>
+      <c r="I63" s="12">
+        <f>I26+I27</f>
+        <v/>
+      </c>
+      <c r="J63" s="12">
+        <f>J26+J27</f>
+        <v/>
+      </c>
+      <c r="K63" s="12">
+        <f>K26+K27</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Liquidez corrente</t>
-        </is>
-      </c>
-      <c r="C64" s="27">
-        <f>C29/C36</f>
-        <v/>
-      </c>
-      <c r="D64" s="27">
-        <f>D29/D36</f>
-        <v/>
-      </c>
-      <c r="E64" s="27">
-        <f>E29/E36</f>
-        <v/>
-      </c>
-      <c r="F64" s="27">
-        <f>F29/F36</f>
-        <v/>
-      </c>
-      <c r="G64" s="27">
-        <f>G29/G36</f>
-        <v/>
-      </c>
-      <c r="H64" s="27">
-        <f>H29/H36</f>
-        <v/>
-      </c>
-      <c r="I64" s="27">
-        <f>I29/I36</f>
-        <v/>
-      </c>
-      <c r="J64" s="27">
-        <f>J29/J36</f>
-        <v/>
-      </c>
-      <c r="K64" s="27">
-        <f>K29/K36</f>
+          <t>Dívida bruta</t>
+        </is>
+      </c>
+      <c r="C64" s="12">
+        <f>C36+C38</f>
+        <v/>
+      </c>
+      <c r="D64" s="12">
+        <f>D36+D38</f>
+        <v/>
+      </c>
+      <c r="E64" s="12">
+        <f>E36+E38</f>
+        <v/>
+      </c>
+      <c r="F64" s="12">
+        <f>F36+F38</f>
+        <v/>
+      </c>
+      <c r="G64" s="12">
+        <f>G36+G38</f>
+        <v/>
+      </c>
+      <c r="H64" s="12">
+        <f>H36+H38</f>
+        <v/>
+      </c>
+      <c r="I64" s="12">
+        <f>I36+I38</f>
+        <v/>
+      </c>
+      <c r="J64" s="12">
+        <f>J36+J38</f>
+        <v/>
+      </c>
+      <c r="K64" s="12">
+        <f>K36+K38</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>ROE (lucro dos controladores / patrimônio dos controladores)</t>
-        </is>
-      </c>
-      <c r="C65" s="11">
-        <f>C18/(C38-C39)</f>
-        <v/>
-      </c>
-      <c r="D65" s="11">
-        <f>D18/(D38-D39)</f>
-        <v/>
-      </c>
-      <c r="E65" s="11">
-        <f>E18/(E38-E39)</f>
-        <v/>
-      </c>
-      <c r="F65" s="11">
-        <f>F18/(F38-F39)</f>
-        <v/>
-      </c>
-      <c r="G65" s="11">
-        <f>G18/(G38-G39)</f>
-        <v/>
-      </c>
-      <c r="H65" s="11">
-        <f>H18/(H38-H39)</f>
-        <v/>
-      </c>
-      <c r="I65" s="11">
-        <f>I18/(I38-I39)</f>
-        <v/>
-      </c>
-      <c r="J65" s="11">
-        <f>J18/(J38-J39)</f>
-        <v/>
-      </c>
-      <c r="K65" s="11">
-        <f>K18/(K38-K39)</f>
+          <t>Dívida líquida</t>
+        </is>
+      </c>
+      <c r="C65" s="12">
+        <f>C64-C63</f>
+        <v/>
+      </c>
+      <c r="D65" s="12">
+        <f>D64-D63</f>
+        <v/>
+      </c>
+      <c r="E65" s="12">
+        <f>E64-E63</f>
+        <v/>
+      </c>
+      <c r="F65" s="12">
+        <f>F64-F63</f>
+        <v/>
+      </c>
+      <c r="G65" s="12">
+        <f>G64-G63</f>
+        <v/>
+      </c>
+      <c r="H65" s="12">
+        <f>H64-H63</f>
+        <v/>
+      </c>
+      <c r="I65" s="12">
+        <f>I64-I63</f>
+        <v/>
+      </c>
+      <c r="J65" s="12">
+        <f>J64-J63</f>
+        <v/>
+      </c>
+      <c r="K65" s="12">
+        <f>K64-K63</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>ROIC (NOPAT / capital de giro + ativo fixo)</t>
-        </is>
-      </c>
-      <c r="C66" s="11">
-        <f>C44/(C59+C52)</f>
-        <v/>
-      </c>
-      <c r="D66" s="11">
-        <f>D44/(D59+D52)</f>
-        <v/>
-      </c>
-      <c r="E66" s="11">
-        <f>E44/(E59+E52)</f>
-        <v/>
-      </c>
-      <c r="F66" s="11">
-        <f>F44/(F59+F52)</f>
-        <v/>
-      </c>
-      <c r="G66" s="11">
-        <f>G44/(G59+G52)</f>
-        <v/>
-      </c>
-      <c r="H66" s="11">
-        <f>H44/(H59+H52)</f>
-        <v/>
-      </c>
-      <c r="I66" s="11">
-        <f>I44/(I59+I52)</f>
-        <v/>
-      </c>
-      <c r="J66" s="11">
-        <f>J44/(J59+J52)</f>
-        <v/>
-      </c>
-      <c r="K66" s="11">
-        <f>K44/(K59+K52)</f>
+          <t>Dívida líquida / EBITDA</t>
+        </is>
+      </c>
+      <c r="C66" s="29">
+        <f>C65/C42</f>
+        <v/>
+      </c>
+      <c r="D66" s="29">
+        <f>D65/D42</f>
+        <v/>
+      </c>
+      <c r="E66" s="29">
+        <f>E65/E42</f>
+        <v/>
+      </c>
+      <c r="F66" s="29">
+        <f>F65/F42</f>
+        <v/>
+      </c>
+      <c r="G66" s="29">
+        <f>G65/G42</f>
+        <v/>
+      </c>
+      <c r="H66" s="29">
+        <f>H65/H42</f>
+        <v/>
+      </c>
+      <c r="I66" s="29">
+        <f>I65/I42</f>
+        <v/>
+      </c>
+      <c r="J66" s="29">
+        <f>J65/J42</f>
+        <v/>
+      </c>
+      <c r="K66" s="29">
+        <f>K65/K42</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
+          <t>Liquidez corrente</t>
+        </is>
+      </c>
+      <c r="C67" s="30">
+        <f>C30/C37</f>
+        <v/>
+      </c>
+      <c r="D67" s="30">
+        <f>D30/D37</f>
+        <v/>
+      </c>
+      <c r="E67" s="30">
+        <f>E30/E37</f>
+        <v/>
+      </c>
+      <c r="F67" s="30">
+        <f>F30/F37</f>
+        <v/>
+      </c>
+      <c r="G67" s="30">
+        <f>G30/G37</f>
+        <v/>
+      </c>
+      <c r="H67" s="30">
+        <f>H30/H37</f>
+        <v/>
+      </c>
+      <c r="I67" s="30">
+        <f>I30/I37</f>
+        <v/>
+      </c>
+      <c r="J67" s="30">
+        <f>J30/J37</f>
+        <v/>
+      </c>
+      <c r="K67" s="30">
+        <f>K30/K37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>ROE (lucro dos controladores / patrimônio dos controladores)</t>
+        </is>
+      </c>
+      <c r="C68" s="11">
+        <f>C19/(C39-C40)</f>
+        <v/>
+      </c>
+      <c r="D68" s="11">
+        <f>D19/(D39-D40)</f>
+        <v/>
+      </c>
+      <c r="E68" s="11">
+        <f>E19/(E39-E40)</f>
+        <v/>
+      </c>
+      <c r="F68" s="11">
+        <f>F19/(F39-F40)</f>
+        <v/>
+      </c>
+      <c r="G68" s="11">
+        <f>G19/(G39-G40)</f>
+        <v/>
+      </c>
+      <c r="H68" s="11">
+        <f>H19/(H39-H40)</f>
+        <v/>
+      </c>
+      <c r="I68" s="11">
+        <f>I19/(I39-I40)</f>
+        <v/>
+      </c>
+      <c r="J68" s="11">
+        <f>J19/(J39-J40)</f>
+        <v/>
+      </c>
+      <c r="K68" s="11">
+        <f>K19/(K39-K40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>ROIC (NOPAT / capital de giro + ativo fixo)</t>
+        </is>
+      </c>
+      <c r="C69" s="11">
+        <f>C47/(C62+C55)</f>
+        <v/>
+      </c>
+      <c r="D69" s="11">
+        <f>D47/(D62+D55)</f>
+        <v/>
+      </c>
+      <c r="E69" s="11">
+        <f>E47/(E62+E55)</f>
+        <v/>
+      </c>
+      <c r="F69" s="11">
+        <f>F47/(F62+F55)</f>
+        <v/>
+      </c>
+      <c r="G69" s="11">
+        <f>G47/(G62+G55)</f>
+        <v/>
+      </c>
+      <c r="H69" s="11">
+        <f>H47/(H62+H55)</f>
+        <v/>
+      </c>
+      <c r="I69" s="11">
+        <f>I47/(I62+I55)</f>
+        <v/>
+      </c>
+      <c r="J69" s="11">
+        <f>J47/(J62+J55)</f>
+        <v/>
+      </c>
+      <c r="K69" s="11">
+        <f>K47/(K62+K55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
           <t>Caixa operacional menos capex</t>
         </is>
       </c>
-      <c r="C67" s="12">
-        <f>C21-C22</f>
-        <v/>
-      </c>
-      <c r="D67" s="12">
-        <f>D21-D22</f>
-        <v/>
-      </c>
-      <c r="E67" s="12">
-        <f>E21-E22</f>
-        <v/>
-      </c>
-      <c r="F67" s="12">
-        <f>F21-F22</f>
-        <v/>
-      </c>
-      <c r="G67" s="12">
-        <f>G21-G22</f>
-        <v/>
-      </c>
-      <c r="H67" s="12">
-        <f>H21-H22</f>
-        <v/>
-      </c>
-      <c r="I67" s="12">
-        <f>I21-I22</f>
-        <v/>
-      </c>
-      <c r="J67" s="12">
-        <f>J21-J22</f>
-        <v/>
-      </c>
-      <c r="K67" s="12">
-        <f>K21-K22</f>
+      <c r="C70" s="12">
+        <f>C22-C23</f>
+        <v/>
+      </c>
+      <c r="D70" s="12">
+        <f>D22-D23</f>
+        <v/>
+      </c>
+      <c r="E70" s="12">
+        <f>E22-E23</f>
+        <v/>
+      </c>
+      <c r="F70" s="12">
+        <f>F22-F23</f>
+        <v/>
+      </c>
+      <c r="G70" s="12">
+        <f>G22-G23</f>
+        <v/>
+      </c>
+      <c r="H70" s="12">
+        <f>H22-H23</f>
+        <v/>
+      </c>
+      <c r="I70" s="12">
+        <f>I22-I23</f>
+        <v/>
+      </c>
+      <c r="J70" s="12">
+        <f>J22-J23</f>
+        <v/>
+      </c>
+      <c r="K70" s="12">
+        <f>K22-K23</f>
         <v/>
       </c>
     </row>
@@ -4589,17 +4364,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Demonstração do resultado</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
@@ -4607,276 +4382,268 @@
           <t>Receita líquida</t>
         </is>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="31">
         <f>'Histórico'!J6</f>
         <v/>
       </c>
-      <c r="D6" s="28">
-        <f>C6*(1+'Premissas'!D29)*(1+'Premissas'!D30)</f>
-        <v/>
-      </c>
-      <c r="E6" s="28">
-        <f>D6*(1+'Premissas'!E29)*(1+'Premissas'!E30)</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>E6*(1+'Premissas'!F29)*(1+'Premissas'!F30)</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>F6*(1+'Premissas'!G29)*(1+'Premissas'!G30)</f>
-        <v/>
-      </c>
-      <c r="H6" s="28">
-        <f>G6*(1+'Premissas'!H29)*(1+'Premissas'!H30)</f>
+      <c r="D6" s="31">
+        <f>C6*(1+'Premissas'!D14)</f>
+        <v/>
+      </c>
+      <c r="E6" s="31">
+        <f>D6*(1+'Premissas'!E14)</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>E6*(1+'Premissas'!F14)</f>
+        <v/>
+      </c>
+      <c r="G6" s="31">
+        <f>F6*(1+'Premissas'!G14)</f>
+        <v/>
+      </c>
+      <c r="H6" s="31">
+        <f>G6*(1+'Premissas'!H14)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>(-) Custo caixa (sem depreciação)</t>
+          <t>(-) Custo dos produtos (sem depreciação)</t>
         </is>
       </c>
       <c r="C7" s="12">
-        <f>-'Histórico'!J42</f>
+        <f>-'Histórico'!J45</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>C7*(1+'Premissas'!D29)*(1+'Premissas'!D31)</f>
+        <f>D6-D8+D9-D10</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>D7*(1+'Premissas'!E29)*(1+'Premissas'!E31)</f>
+        <f>E6-E8+E9-E10</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>E7*(1+'Premissas'!F29)*(1+'Premissas'!F31)</f>
+        <f>F6-F8+F9-F10</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>F7*(1+'Premissas'!G29)*(1+'Premissas'!G31)</f>
+        <f>G6-G8+G9-G10</f>
         <v/>
       </c>
       <c r="H7" s="12">
-        <f>G7*(1+'Premissas'!H29)*(1+'Premissas'!H31)</f>
+        <f>H6-H8+H9-H10</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>(-) Despesas com vendas</t>
+          <t>(-) Despesas operacionais (vendas, administrativas e outras)</t>
         </is>
       </c>
       <c r="C8" s="12">
-        <f>-'Histórico'!J9</f>
+        <f>-('Histórico'!J9+'Histórico'!J10+'Histórico'!J46)</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>C8*(1+'Premissas'!D29)*(1+'Premissas'!D31)</f>
+        <f>D6*'Premissas'!D18</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>D8*(1+'Premissas'!E29)*(1+'Premissas'!E31)</f>
+        <f>E6*'Premissas'!E18</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>E8*(1+'Premissas'!F29)*(1+'Premissas'!F31)</f>
+        <f>F6*'Premissas'!F18</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>F8*(1+'Premissas'!G29)*(1+'Premissas'!G31)</f>
+        <f>G6*'Premissas'!G18</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>G8*(1+'Premissas'!H29)*(1+'Premissas'!H31)</f>
+        <f>H6*'Premissas'!H18</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>(-) Despesas gerais e administrativas</t>
+          <t>(+/-) Equivalência patrimonial</t>
         </is>
       </c>
       <c r="C9" s="12">
-        <f>-'Histórico'!J10</f>
+        <f>'Histórico'!J13</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>C9*(1+'Premissas'!D31)</f>
+        <f>'Premissas'!D19</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>D9*(1+'Premissas'!E31)</f>
+        <f>'Premissas'!E19</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>E9*(1+'Premissas'!F31)</f>
+        <f>'Premissas'!F19</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>F9*(1+'Premissas'!G31)</f>
+        <f>'Premissas'!G19</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>G9*(1+'Premissas'!H31)</f>
+        <f>'Premissas'!H19</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>(+/-) Outras receitas/despesas operacionais</t>
-        </is>
-      </c>
-      <c r="C10" s="12">
-        <f>'Histórico'!J43</f>
-        <v/>
-      </c>
-      <c r="D10" s="12">
-        <f>D6*'Premissas'!D32</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
-        <f>E6*'Premissas'!E32</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>F6*'Premissas'!F32</f>
-        <v/>
-      </c>
-      <c r="G10" s="12">
-        <f>G6*'Premissas'!G32</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>H6*'Premissas'!H32</f>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C10" s="31">
+        <f>C6-C7-C8+C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="31">
+        <f>D6*'Premissas'!D15</f>
+        <v/>
+      </c>
+      <c r="E10" s="31">
+        <f>E6*'Premissas'!E15</f>
+        <v/>
+      </c>
+      <c r="F10" s="31">
+        <f>F6*'Premissas'!F15</f>
+        <v/>
+      </c>
+      <c r="G10" s="31">
+        <f>G6*'Premissas'!G15</f>
+        <v/>
+      </c>
+      <c r="H10" s="31">
+        <f>H6*'Premissas'!H15</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>(+/-) Equivalência patrimonial</t>
+          <t>(-) Depreciação e amortização</t>
         </is>
       </c>
       <c r="C11" s="12">
-        <f>'Histórico'!J12</f>
+        <f>'Histórico'!J21</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>'Premissas'!D33</f>
+        <f>C23*'Premissas'!D21</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>'Premissas'!E33</f>
+        <f>D23*'Premissas'!E21</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>'Premissas'!F33</f>
+        <f>E23*'Premissas'!F21</f>
         <v/>
       </c>
       <c r="G11" s="12">
-        <f>'Premissas'!G33</f>
+        <f>F23*'Premissas'!G21</f>
         <v/>
       </c>
       <c r="H11" s="12">
-        <f>'Premissas'!H33</f>
+        <f>G23*'Premissas'!H21</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C12" s="28">
-        <f>C6-C7-C8-C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>D6-D7-D8-D9+D10+D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>E6-E7-E8-E9+E10+E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>F6-F7-F8-F9+F10+F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>G6-G7-G8-G9+G10+G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>H6-H7-H8-H9+H10+H11</f>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C12" s="31">
+        <f>C10-C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="31">
+        <f>D10-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="31">
+        <f>E10-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="31">
+        <f>F10-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="31">
+        <f>G10-G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="31">
+        <f>H10-H11</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>(-) Depreciação e amortização</t>
-        </is>
-      </c>
-      <c r="C13" s="12">
-        <f>'Histórico'!J20</f>
-        <v/>
+          <t>(+) Rendimento do caixa</t>
+        </is>
       </c>
       <c r="D13" s="12">
-        <f>C23*'Premissas'!D35</f>
+        <f>C38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>D23*'Premissas'!E35</f>
+        <f>D38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>E23*'Premissas'!F35</f>
+        <f>E38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="G13" s="12">
-        <f>F23*'Premissas'!G35</f>
+        <f>F38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="H13" s="12">
-        <f>G23*'Premissas'!H35</f>
+        <f>G38*'Premissas'!$D$30</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C14" s="28">
-        <f>C12-C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="28">
-        <f>D12-D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="28">
-        <f>E12-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="28">
-        <f>F12-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="28">
-        <f>G12-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="28">
-        <f>H12-H13</f>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>(-) Juros da dívida</t>
+        </is>
+      </c>
+      <c r="D14" s="12">
+        <f>C42*'Premissas'!$D$29</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>D42*'Premissas'!$D$29</f>
+        <v/>
+      </c>
+      <c r="F14" s="12">
+        <f>E42*'Premissas'!$D$29</f>
+        <v/>
+      </c>
+      <c r="G14" s="12">
+        <f>F42*'Premissas'!$D$29</f>
+        <v/>
+      </c>
+      <c r="H14" s="12">
+        <f>G42*'Premissas'!$D$29</f>
         <v/>
       </c>
     </row>
@@ -4887,27 +4654,27 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>'Histórico'!J14</f>
+        <f>'Histórico'!J15</f>
         <v/>
       </c>
       <c r="D15" s="12">
-        <f>C38*'Premissas'!$D$44-C42*'Premissas'!$D$43</f>
+        <f>D13-D14</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>D38*'Premissas'!$D$44-D42*'Premissas'!$D$43</f>
+        <f>E13-E14</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>E38*'Premissas'!$D$44-E42*'Premissas'!$D$43</f>
+        <f>F13-F14</f>
         <v/>
       </c>
       <c r="G15" s="12">
-        <f>F38*'Premissas'!$D$44-F42*'Premissas'!$D$43</f>
+        <f>G13-G14</f>
         <v/>
       </c>
       <c r="H15" s="12">
-        <f>G38*'Premissas'!$D$44-G42*'Premissas'!$D$43</f>
+        <f>H13-H14</f>
         <v/>
       </c>
     </row>
@@ -4918,27 +4685,27 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>C14+C15</f>
+        <f>C12+C15</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>D14+D15</f>
+        <f>D12+D15</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>E14+E15</f>
+        <f>E12+E15</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>F14+F15</f>
+        <f>F12+F15</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>G14+G15</f>
+        <f>G12+G15</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>H14+H15</f>
+        <f>H12+H15</f>
         <v/>
       </c>
     </row>
@@ -4949,27 +4716,27 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>-'Histórico'!J16</f>
+        <f>-'Histórico'!J17</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>MAX(0,D16-D11)*'Premissas'!$D$42</f>
+        <f>MAX(0,D16-D9)*'Premissas'!$D$28</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>MAX(0,E16-E11)*'Premissas'!$D$42</f>
+        <f>MAX(0,E16-E9)*'Premissas'!$D$28</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>MAX(0,F16-F11)*'Premissas'!$D$42</f>
+        <f>MAX(0,F16-F9)*'Premissas'!$D$28</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>MAX(0,G16-G11)*'Premissas'!$D$42</f>
+        <f>MAX(0,G16-G9)*'Premissas'!$D$28</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>MAX(0,H16-H11)*'Premissas'!$D$42</f>
+        <f>MAX(0,H16-H9)*'Premissas'!$D$28</f>
         <v/>
       </c>
     </row>
@@ -4979,27 +4746,27 @@
           <t>Lucro líquido</t>
         </is>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="31">
         <f>C16-C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="31">
         <f>D16-D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="31">
         <f>E16-E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="31">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="31">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="31">
         <f>H16-H17</f>
         <v/>
       </c>
@@ -5011,42 +4778,42 @@
         </is>
       </c>
       <c r="C19" s="12">
-        <f>(C14-C11)*(1-'Premissas'!$D$42)</f>
+        <f>(C12-C9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>(D14-D11)*(1-'Premissas'!$D$42)</f>
+        <f>(D12-D9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>(E14-E11)*(1-'Premissas'!$D$42)</f>
+        <f>(E12-E9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>(F14-F11)*(1-'Premissas'!$D$42)</f>
+        <f>(F12-F9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
       <c r="G19" s="12">
-        <f>(G14-G11)*(1-'Premissas'!$D$42)</f>
+        <f>(G12-G9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
       <c r="H19" s="12">
-        <f>(H14-H11)*(1-'Premissas'!$D$42)</f>
+        <f>(H12-H9)*(1-'Premissas'!$D$28)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Investimento, depreciação e capital de giro</t>
         </is>
       </c>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="27" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
@@ -5055,27 +4822,27 @@
         </is>
       </c>
       <c r="C22" s="12">
-        <f>'Histórico'!J22</f>
+        <f>'Histórico'!J23</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>D6*'Premissas'!D34</f>
+        <f>D6*'Premissas'!D20</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>E6*'Premissas'!E34</f>
+        <f>E6*'Premissas'!E20</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>F6*'Premissas'!F34</f>
+        <f>F6*'Premissas'!F20</f>
         <v/>
       </c>
       <c r="G22" s="12">
-        <f>G6*'Premissas'!G34</f>
+        <f>G6*'Premissas'!G20</f>
         <v/>
       </c>
       <c r="H22" s="12">
-        <f>H6*'Premissas'!H34</f>
+        <f>H6*'Premissas'!H20</f>
         <v/>
       </c>
     </row>
@@ -5086,27 +4853,27 @@
         </is>
       </c>
       <c r="C23" s="12">
-        <f>'Histórico'!J52</f>
+        <f>'Histórico'!J55</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>C23+D22-D13</f>
+        <f>C23+D22-D11</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>D23+E22-E13</f>
+        <f>D23+E22-E11</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>E23+F22-F13</f>
+        <f>E23+F22-F11</f>
         <v/>
       </c>
       <c r="G23" s="12">
-        <f>F23+G22-G13</f>
+        <f>F23+G22-G11</f>
         <v/>
       </c>
       <c r="H23" s="12">
-        <f>G23+H22-H13</f>
+        <f>G23+H22-H11</f>
         <v/>
       </c>
     </row>
@@ -5117,27 +4884,27 @@
         </is>
       </c>
       <c r="C24" s="12">
-        <f>'Histórico'!J27</f>
+        <f>'Histórico'!J28</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>D6*'Premissas'!D36/365</f>
+        <f>D6*'Premissas'!D22/365</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>E6*'Premissas'!E36/365</f>
+        <f>E6*'Premissas'!E22/365</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>F6*'Premissas'!F36/365</f>
+        <f>F6*'Premissas'!F22/365</f>
         <v/>
       </c>
       <c r="G24" s="12">
-        <f>G6*'Premissas'!G36/365</f>
+        <f>G6*'Premissas'!G22/365</f>
         <v/>
       </c>
       <c r="H24" s="12">
-        <f>H6*'Premissas'!H36/365</f>
+        <f>H6*'Premissas'!H22/365</f>
         <v/>
       </c>
     </row>
@@ -5148,27 +4915,27 @@
         </is>
       </c>
       <c r="C25" s="12">
-        <f>'Histórico'!J28</f>
+        <f>'Histórico'!J29</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>D7*'Premissas'!D37/365</f>
+        <f>D7*'Premissas'!D23/365</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>E7*'Premissas'!E37/365</f>
+        <f>E7*'Premissas'!E23/365</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>F7*'Premissas'!F37/365</f>
+        <f>F7*'Premissas'!F23/365</f>
         <v/>
       </c>
       <c r="G25" s="12">
-        <f>G7*'Premissas'!G37/365</f>
+        <f>G7*'Premissas'!G23/365</f>
         <v/>
       </c>
       <c r="H25" s="12">
-        <f>H7*'Premissas'!H37/365</f>
+        <f>H7*'Premissas'!H23/365</f>
         <v/>
       </c>
     </row>
@@ -5179,27 +4946,27 @@
         </is>
       </c>
       <c r="C26" s="12">
-        <f>'Histórico'!J34</f>
+        <f>'Histórico'!J35</f>
         <v/>
       </c>
       <c r="D26" s="12">
-        <f>D7*'Premissas'!D38/365</f>
+        <f>D7*'Premissas'!D24/365</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>E7*'Premissas'!E38/365</f>
+        <f>E7*'Premissas'!E24/365</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>F7*'Premissas'!F38/365</f>
+        <f>F7*'Premissas'!F24/365</f>
         <v/>
       </c>
       <c r="G26" s="12">
-        <f>G7*'Premissas'!G38/365</f>
+        <f>G7*'Premissas'!G24/365</f>
         <v/>
       </c>
       <c r="H26" s="12">
-        <f>H7*'Premissas'!H38/365</f>
+        <f>H7*'Premissas'!H24/365</f>
         <v/>
       </c>
     </row>
@@ -5209,27 +4976,27 @@
           <t>Capital de giro</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="31">
         <f>C24+C25-C26</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="31">
         <f>D24+D25-D26</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="31">
         <f>E24+E25-E26</f>
         <v/>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="31">
         <f>F24+F25-F26</f>
         <v/>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="31">
         <f>G24+G25-G26</f>
         <v/>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="31">
         <f>H24+H25-H26</f>
         <v/>
       </c>
@@ -5262,17 +5029,17 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Fluxos de caixa livres</t>
         </is>
       </c>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
+      <c r="H30" s="27" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="8" t="inlineStr">
@@ -5280,24 +5047,24 @@
           <t>FCFF - fluxo de caixa livre da empresa</t>
         </is>
       </c>
-      <c r="D31" s="28">
-        <f>D19+D13-D22-D28</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>E19+E13-E22-E28</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>F19+F13-F22-F28</f>
-        <v/>
-      </c>
-      <c r="G31" s="28">
-        <f>G19+G13-G22-G28</f>
-        <v/>
-      </c>
-      <c r="H31" s="28">
-        <f>H19+H13-H22-H28</f>
+      <c r="D31" s="31">
+        <f>D19+D11-D22-D28</f>
+        <v/>
+      </c>
+      <c r="E31" s="31">
+        <f>E19+E11-E22-E28</f>
+        <v/>
+      </c>
+      <c r="F31" s="31">
+        <f>F19+F11-F22-F28</f>
+        <v/>
+      </c>
+      <c r="G31" s="31">
+        <f>G19+G11-G22-G28</f>
+        <v/>
+      </c>
+      <c r="H31" s="31">
+        <f>H19+H11-H22-H28</f>
         <v/>
       </c>
     </row>
@@ -5308,23 +5075,23 @@
         </is>
       </c>
       <c r="D32" s="12">
-        <f>'Premissas'!D39</f>
+        <f>'Premissas'!D25</f>
         <v/>
       </c>
       <c r="E32" s="12">
-        <f>'Premissas'!E39</f>
+        <f>'Premissas'!E25</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>'Premissas'!F39</f>
+        <f>'Premissas'!F25</f>
         <v/>
       </c>
       <c r="G32" s="12">
-        <f>'Premissas'!G39</f>
+        <f>'Premissas'!G25</f>
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>'Premissas'!H39</f>
+        <f>'Premissas'!H25</f>
         <v/>
       </c>
     </row>
@@ -5334,24 +5101,24 @@
           <t>FCFE - fluxo de caixa livre do acionista</t>
         </is>
       </c>
-      <c r="D33" s="28">
-        <f>D18-D11+D13-D22-D28+D32</f>
-        <v/>
-      </c>
-      <c r="E33" s="28">
-        <f>E18-E11+E13-E22-E28+E32</f>
-        <v/>
-      </c>
-      <c r="F33" s="28">
-        <f>F18-F11+F13-F22-F28+F32</f>
-        <v/>
-      </c>
-      <c r="G33" s="28">
-        <f>G18-G11+G13-G22-G28+G32</f>
-        <v/>
-      </c>
-      <c r="H33" s="28">
-        <f>H18-H11+H13-H22-H28+H32</f>
+      <c r="D33" s="31">
+        <f>D18-D9+D11-D22-D28+D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="31">
+        <f>E18-E9+E11-E22-E28+E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="31">
+        <f>F18-F9+F11-F22-F28+F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="31">
+        <f>G18-G9+G11-G22-G28+G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="31">
+        <f>H18-H9+H11-H22-H28+H32</f>
         <v/>
       </c>
     </row>
@@ -5362,23 +5129,23 @@
         </is>
       </c>
       <c r="D34" s="12">
-        <f>MAX(0,D18)*'Premissas'!$D$45</f>
+        <f>MAX(0,D18)*'Premissas'!$D$31</f>
         <v/>
       </c>
       <c r="E34" s="12">
-        <f>MAX(0,E18)*'Premissas'!$D$45</f>
+        <f>MAX(0,E18)*'Premissas'!$D$31</f>
         <v/>
       </c>
       <c r="F34" s="12">
-        <f>MAX(0,F18)*'Premissas'!$D$45</f>
+        <f>MAX(0,F18)*'Premissas'!$D$31</f>
         <v/>
       </c>
       <c r="G34" s="12">
-        <f>MAX(0,G18)*'Premissas'!$D$45</f>
+        <f>MAX(0,G18)*'Premissas'!$D$31</f>
         <v/>
       </c>
       <c r="H34" s="12">
-        <f>MAX(0,H18)*'Premissas'!$D$45</f>
+        <f>MAX(0,H18)*'Premissas'!$D$31</f>
         <v/>
       </c>
     </row>
@@ -5410,17 +5177,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="24" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Balanço patrimonial resumido</t>
         </is>
       </c>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
+      <c r="C37" s="27" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="27" t="n"/>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="27" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
@@ -5429,7 +5196,7 @@
         </is>
       </c>
       <c r="C38" s="12">
-        <f>'Histórico'!J60</f>
+        <f>'Histórico'!J63</f>
         <v/>
       </c>
       <c r="D38" s="12">
@@ -5460,27 +5227,27 @@
         </is>
       </c>
       <c r="C39" s="12">
-        <f>'Histórico'!J30</f>
+        <f>'Histórico'!J31</f>
         <v/>
       </c>
       <c r="D39" s="12">
-        <f>C39+D11</f>
+        <f>C39+D9</f>
         <v/>
       </c>
       <c r="E39" s="12">
-        <f>D39+E11</f>
+        <f>D39+E9</f>
         <v/>
       </c>
       <c r="F39" s="12">
-        <f>E39+F11</f>
+        <f>E39+F9</f>
         <v/>
       </c>
       <c r="G39" s="12">
-        <f>F39+G11</f>
+        <f>F39+G9</f>
         <v/>
       </c>
       <c r="H39" s="12">
-        <f>G39+H11</f>
+        <f>G39+H9</f>
         <v/>
       </c>
     </row>
@@ -5491,7 +5258,7 @@
         </is>
       </c>
       <c r="C40" s="12">
-        <f>'Histórico'!J33-C38-C24-C25-C23-C39</f>
+        <f>'Histórico'!J34-C38-C24-C25-C23-C39</f>
         <v/>
       </c>
       <c r="D40" s="12">
@@ -5521,27 +5288,27 @@
           <t>Ativo total</t>
         </is>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="31">
         <f>C38+C24+C25+C23+C39+C40</f>
         <v/>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="31">
         <f>D38+D24+D25+D23+D39+D40</f>
         <v/>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="31">
         <f>E38+E24+E25+E23+E39+E40</f>
         <v/>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="31">
         <f>F38+F24+F25+F23+F39+F40</f>
         <v/>
       </c>
-      <c r="G41" s="28">
+      <c r="G41" s="31">
         <f>G38+G24+G25+G23+G39+G40</f>
         <v/>
       </c>
-      <c r="H41" s="28">
+      <c r="H41" s="31">
         <f>H38+H24+H25+H23+H39+H40</f>
         <v/>
       </c>
@@ -5553,7 +5320,7 @@
         </is>
       </c>
       <c r="C42" s="12">
-        <f>'Histórico'!J61</f>
+        <f>'Histórico'!J64</f>
         <v/>
       </c>
       <c r="D42" s="12">
@@ -5584,7 +5351,7 @@
         </is>
       </c>
       <c r="C43" s="12">
-        <f>'Histórico'!J33-C26-C42-C44</f>
+        <f>'Histórico'!J34-C26-C42-C44</f>
         <v/>
       </c>
       <c r="D43" s="12">
@@ -5615,7 +5382,7 @@
         </is>
       </c>
       <c r="C44" s="12">
-        <f>'Histórico'!J38</f>
+        <f>'Histórico'!J39</f>
         <v/>
       </c>
       <c r="D44" s="12">
@@ -5645,27 +5412,27 @@
           <t>Passivo + patrimônio líquido</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="31">
         <f>C26+C42+C43+C44</f>
         <v/>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="31">
         <f>D26+D42+D43+D44</f>
         <v/>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="31">
         <f>E26+E42+E43+E44</f>
         <v/>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="31">
         <f>F26+F42+F43+F44</f>
         <v/>
       </c>
-      <c r="G45" s="28">
+      <c r="G45" s="31">
         <f>G26+G42+G43+G44</f>
         <v/>
       </c>
-      <c r="H45" s="28">
+      <c r="H45" s="31">
         <f>H26+H42+H43+H44</f>
         <v/>
       </c>
@@ -5702,17 +5469,17 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="24" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>Indicadores</t>
         </is>
       </c>
-      <c r="C48" s="25" t="n"/>
-      <c r="D48" s="25" t="n"/>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
+      <c r="C48" s="27" t="n"/>
+      <c r="D48" s="27" t="n"/>
+      <c r="E48" s="27" t="n"/>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="27" t="n"/>
+      <c r="H48" s="27" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
@@ -5748,27 +5515,27 @@
         </is>
       </c>
       <c r="C50" s="11">
-        <f>C12/C6</f>
+        <f>C10/C6</f>
         <v/>
       </c>
       <c r="D50" s="11">
-        <f>D12/D6</f>
+        <f>D10/D6</f>
         <v/>
       </c>
       <c r="E50" s="11">
-        <f>E12/E6</f>
+        <f>E10/E6</f>
         <v/>
       </c>
       <c r="F50" s="11">
-        <f>F12/F6</f>
+        <f>F10/F6</f>
         <v/>
       </c>
       <c r="G50" s="11">
-        <f>G12/G6</f>
+        <f>G10/G6</f>
         <v/>
       </c>
       <c r="H50" s="11">
-        <f>H12/H6</f>
+        <f>H10/H6</f>
         <v/>
       </c>
     </row>
@@ -5779,27 +5546,27 @@
         </is>
       </c>
       <c r="C51" s="11">
-        <f>C14/C6</f>
+        <f>C12/C6</f>
         <v/>
       </c>
       <c r="D51" s="11">
-        <f>D14/D6</f>
+        <f>D12/D6</f>
         <v/>
       </c>
       <c r="E51" s="11">
-        <f>E14/E6</f>
+        <f>E12/E6</f>
         <v/>
       </c>
       <c r="F51" s="11">
-        <f>F14/F6</f>
+        <f>F12/F6</f>
         <v/>
       </c>
       <c r="G51" s="11">
-        <f>G14/G6</f>
+        <f>G12/G6</f>
         <v/>
       </c>
       <c r="H51" s="11">
-        <f>H14/H6</f>
+        <f>H12/H6</f>
         <v/>
       </c>
     </row>
@@ -5840,28 +5607,28 @@
           <t>Dívida líquida / EBITDA</t>
         </is>
       </c>
-      <c r="C53" s="26">
-        <f>C52/C12</f>
-        <v/>
-      </c>
-      <c r="D53" s="26">
-        <f>D52/D12</f>
-        <v/>
-      </c>
-      <c r="E53" s="26">
-        <f>E52/E12</f>
-        <v/>
-      </c>
-      <c r="F53" s="26">
-        <f>F52/F12</f>
-        <v/>
-      </c>
-      <c r="G53" s="26">
-        <f>G52/G12</f>
-        <v/>
-      </c>
-      <c r="H53" s="26">
-        <f>H52/H12</f>
+      <c r="C53" s="29">
+        <f>C52/C10</f>
+        <v/>
+      </c>
+      <c r="D53" s="29">
+        <f>D52/D10</f>
+        <v/>
+      </c>
+      <c r="E53" s="29">
+        <f>E52/E10</f>
+        <v/>
+      </c>
+      <c r="F53" s="29">
+        <f>F52/F10</f>
+        <v/>
+      </c>
+      <c r="G53" s="29">
+        <f>G52/G10</f>
+        <v/>
+      </c>
+      <c r="H53" s="29">
+        <f>H52/H10</f>
         <v/>
       </c>
     </row>
@@ -5898,1099 +5665,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:E24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Custo de capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CAPM para o capital próprio; WACC é a média com o custo da dívida depois do imposto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Capital próprio (CAPM)</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Conta</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Juro sem risco (Rf)</t>
-        </is>
-      </c>
-      <c r="D5" s="11">
-        <f>'Premissas'!$D$46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="D6" s="27">
-        <f>'Premissas'!$D$47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio de risco de mercado</t>
-        </is>
-      </c>
-      <c r="D7" s="11">
-        <f>'Premissas'!$D$48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio adicional</t>
-        </is>
-      </c>
-      <c r="D8" s="11">
-        <f>'Premissas'!$D$49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Custo do capital próprio (Ke)</t>
-        </is>
-      </c>
-      <c r="D9" s="29">
-        <f>D5+D6*D7+D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Ke = Rf + beta x prêmio de mercado + prêmio adicional</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Dívida</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Conta</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Custo da dívida antes do imposto (Kd)</t>
-        </is>
-      </c>
-      <c r="D12" s="11">
-        <f>'Premissas'!$D$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Alíquota de IR e CSLL</t>
-        </is>
-      </c>
-      <c r="D13" s="11">
-        <f>'Premissas'!$D$42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Custo da dívida após o imposto</t>
-        </is>
-      </c>
-      <c r="D14" s="29">
-        <f>D12*(1-D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Juro é dedutível: Kd x (1 - alíquota)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Média ponderada</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Conta</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Peso da dívida</t>
-        </is>
-      </c>
-      <c r="D17" s="11">
-        <f>'Premissas'!$D$50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Peso do capital próprio</t>
-        </is>
-      </c>
-      <c r="D18" s="11">
-        <f>1-D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="D19" s="30">
-        <f>D9*D18+D14*D17</f>
-        <v/>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>WACC = Ke x peso do capital próprio + Kd após imposto x peso da dívida</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Referência: estrutura a valor de mercado</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Conta</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Valor de mercado (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D22" s="12">
-        <f>'Premissas'!$D$60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Dívida bruta na data-base (R$ milhões)</t>
-        </is>
-      </c>
-      <c r="D23" s="12">
-        <f>'Histórico'!K61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Peso da dívida a valor de mercado</t>
-        </is>
-      </c>
-      <c r="D24" s="11">
-        <f>D23/(D23+D22)</f>
-        <v/>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Compare com o peso usado acima.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B1:I52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fluxo de caixa descontado - Vale</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>O valor da empresa é a soma dos fluxos de caixa futuros trazidos a valor de hoje.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>R$ milhões</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Fluxo da empresa (FCFF), descontado pelo WACC</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>FCFF</t>
-        </is>
-      </c>
-      <c r="D6" s="28">
-        <f>'Projeção'!D31</f>
-        <v/>
-      </c>
-      <c r="E6" s="28">
-        <f>'Projeção'!E31</f>
-        <v/>
-      </c>
-      <c r="F6" s="28">
-        <f>'Projeção'!F31</f>
-        <v/>
-      </c>
-      <c r="G6" s="28">
-        <f>'Projeção'!G31</f>
-        <v/>
-      </c>
-      <c r="H6" s="28">
-        <f>'Projeção'!H31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Parte do ano que entra no valor</t>
-        </is>
-      </c>
-      <c r="D7" s="31">
-        <f>'Premissas'!$D$57</f>
-        <v/>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Fim do período (anos desde a data-base)</t>
-        </is>
-      </c>
-      <c r="D8" s="31">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="31">
-        <f>D8+1</f>
-        <v/>
-      </c>
-      <c r="F8" s="31">
-        <f>E8+1</f>
-        <v/>
-      </c>
-      <c r="G8" s="31">
-        <f>F8+1</f>
-        <v/>
-      </c>
-      <c r="H8" s="31">
-        <f>G8+1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Meio do período (quando o caixa entra, em média)</t>
-        </is>
-      </c>
-      <c r="D9" s="31">
-        <f>D8-D7/2</f>
-        <v/>
-      </c>
-      <c r="E9" s="31">
-        <f>E8-E7/2</f>
-        <v/>
-      </c>
-      <c r="F9" s="31">
-        <f>F8-F7/2</f>
-        <v/>
-      </c>
-      <c r="G9" s="31">
-        <f>G8-G7/2</f>
-        <v/>
-      </c>
-      <c r="H9" s="31">
-        <f>H8-H7/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Fator de desconto</t>
-        </is>
-      </c>
-      <c r="D10" s="32">
-        <f>1/(1+'WACC'!$D$19)^D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>1/(1+'WACC'!$D$19)^E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="32">
-        <f>1/(1+'WACC'!$D$19)^F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>1/(1+'WACC'!$D$19)^G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="32">
-        <f>1/(1+'WACC'!$D$19)^H9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Valor presente do fluxo</t>
-        </is>
-      </c>
-      <c r="D11" s="28">
-        <f>D6*D7*D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="28">
-        <f>E6*E7*E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>F6*F7*F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>G6*G7*G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>H6*H7*H10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Perpetuidade (Gordon)</t>
-        </is>
-      </c>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="25" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="D14" s="11">
-        <f>'WACC'!$D$19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Crescimento na perpetuidade (g)</t>
-        </is>
-      </c>
-      <c r="D15" s="11">
-        <f>'Premissas'!$D$51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>FCFF normalizado de 2030</t>
-        </is>
-      </c>
-      <c r="D16" s="12">
-        <f>'Projeção'!H19+'Projeção'!H13-'Premissas'!$D$52*'Projeção'!H13-'Projeção'!H28</f>
-        <v/>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>NOPAT + depreciação - capex de reposição - investimento em giro</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Valor terminal no fim do último ano</t>
-        </is>
-      </c>
-      <c r="D17" s="12">
-        <f>D16*(1+D15)/(D14-D15)</f>
-        <v/>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>FCFF x (1 + g) / (WACC - g)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Valor presente do valor terminal</t>
-        </is>
-      </c>
-      <c r="D18" s="12">
-        <f>D17/(1+D14)^H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Do valor da empresa ao preço por ação</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Valor presente dos fluxos projetados</t>
-        </is>
-      </c>
-      <c r="D21" s="12">
-        <f>SUM($D$11:$H$11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>(+) Valor presente do valor terminal</t>
-        </is>
-      </c>
-      <c r="D22" s="12">
-        <f>D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Valor da empresa (Enterprise Value)</t>
-        </is>
-      </c>
-      <c r="D23" s="28">
-        <f>D21+D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>(-) Dívida líquida na data-base</t>
-        </is>
-      </c>
-      <c r="D24" s="12">
-        <f>'Histórico'!K62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>(-) Participação de não controladores</t>
-        </is>
-      </c>
-      <c r="D25" s="12">
-        <f>'Histórico'!K39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>(+) Investimentos em coligadas (valor contábil)</t>
-        </is>
-      </c>
-      <c r="D26" s="12">
-        <f>'Histórico'!K30</f>
-        <v/>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>O FCFF não inclui a equivalência; as coligadas entram pelo valor do balanço.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>(-) Outros passivos tratados como dívida</t>
-        </is>
-      </c>
-      <c r="D27" s="12">
-        <f>'Premissas'!$D$53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Valor do acionista (Equity Value)</t>
-        </is>
-      </c>
-      <c r="D28" s="28">
-        <f>D23-D24-D25+D26-D27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Ações em circulação (milhões)</t>
-        </is>
-      </c>
-      <c r="D29" s="33">
-        <f>'Premissas'!$D$58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Preço justo por ação</t>
-        </is>
-      </c>
-      <c r="D30" s="9">
-        <f>D28/D29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Preço de mercado</t>
-        </is>
-      </c>
-      <c r="D31" s="10">
-        <f>'Premissas'!$D$59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Diferença para o preço de mercado</t>
-        </is>
-      </c>
-      <c r="D32" s="11">
-        <f>D30/D31-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Peso do valor terminal no valor da empresa</t>
-        </is>
-      </c>
-      <c r="D33" s="11">
-        <f>D18/D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>EV / EBITDA 2026E implícito</t>
-        </is>
-      </c>
-      <c r="D34" s="26">
-        <f>D23/'Projeção'!D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>Conferência pelo fluxo do acionista (FCFE), descontado pelo Ke</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="25" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>FCFE</t>
-        </is>
-      </c>
-      <c r="D37" s="28">
-        <f>'Projeção'!D33</f>
-        <v/>
-      </c>
-      <c r="E37" s="28">
-        <f>'Projeção'!E33</f>
-        <v/>
-      </c>
-      <c r="F37" s="28">
-        <f>'Projeção'!F33</f>
-        <v/>
-      </c>
-      <c r="G37" s="28">
-        <f>'Projeção'!G33</f>
-        <v/>
-      </c>
-      <c r="H37" s="28">
-        <f>'Projeção'!H33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Fator de desconto</t>
-        </is>
-      </c>
-      <c r="D38" s="32">
-        <f>1/(1+'WACC'!$D$9)^D9</f>
-        <v/>
-      </c>
-      <c r="E38" s="32">
-        <f>1/(1+'WACC'!$D$9)^E9</f>
-        <v/>
-      </c>
-      <c r="F38" s="32">
-        <f>1/(1+'WACC'!$D$9)^F9</f>
-        <v/>
-      </c>
-      <c r="G38" s="32">
-        <f>1/(1+'WACC'!$D$9)^G9</f>
-        <v/>
-      </c>
-      <c r="H38" s="32">
-        <f>1/(1+'WACC'!$D$9)^H9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Valor presente do fluxo</t>
-        </is>
-      </c>
-      <c r="D39" s="12">
-        <f>D37*D7*D38</f>
-        <v/>
-      </c>
-      <c r="E39" s="12">
-        <f>E37*E7*E38</f>
-        <v/>
-      </c>
-      <c r="F39" s="12">
-        <f>F37*F7*F38</f>
-        <v/>
-      </c>
-      <c r="G39" s="12">
-        <f>G37*G7*G38</f>
-        <v/>
-      </c>
-      <c r="H39" s="12">
-        <f>H37*H7*H38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Custo do capital próprio (Ke)</t>
-        </is>
-      </c>
-      <c r="D40" s="11">
-        <f>'WACC'!$D$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>FCFE normalizado de 2030</t>
-        </is>
-      </c>
-      <c r="D41" s="12">
-        <f>'Projeção'!H18-'Projeção'!H11+'Projeção'!H13-'Premissas'!$D$52*'Projeção'!H13-'Projeção'!H28+'Projeção'!H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Valor presente do valor terminal</t>
-        </is>
-      </c>
-      <c r="D42" s="12">
-        <f>D41*(1+D15)/(D40-D15)/(1+D40)^H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Valor do acionista pelo FCFE</t>
-        </is>
-      </c>
-      <c r="D43" s="28">
-        <f>SUM($D$39:$H$39)+D42-D25+D26-D27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Preço por ação pelo FCFE</t>
-        </is>
-      </c>
-      <c r="D44" s="10">
-        <f>D43/D29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>Sensibilidade do preço justo: WACC (linhas) x crescimento perpétuo (colunas)</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="n"/>
-      <c r="D46" s="25" t="n"/>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="25" t="n"/>
-      <c r="G46" s="25" t="n"/>
-      <c r="H46" s="25" t="n"/>
-    </row>
-    <row r="47">
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>WACC \ g</t>
-        </is>
-      </c>
-      <c r="D47" s="35">
-        <f>$D$15+-2*0.005</f>
-        <v/>
-      </c>
-      <c r="E47" s="35">
-        <f>$D$15+-1*0.005</f>
-        <v/>
-      </c>
-      <c r="F47" s="35">
-        <f>$D$15+0*0.005</f>
-        <v/>
-      </c>
-      <c r="G47" s="35">
-        <f>$D$15+1*0.005</f>
-        <v/>
-      </c>
-      <c r="H47" s="35">
-        <f>$D$15+2*0.005</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="35">
-        <f>$D$14+-2*0.01</f>
-        <v/>
-      </c>
-      <c r="D48" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+D$47)/($C48-D$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="E48" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+E$47)/($C48-E$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+F$47)/($C48-F$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="G48" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+G$47)/($C48-G$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="H48" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+H$47)/($C48-H$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="35">
-        <f>$D$14+-1*0.01</f>
-        <v/>
-      </c>
-      <c r="D49" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+D$47)/($C49-D$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="E49" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+E$47)/($C49-E$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+F$47)/($C49-F$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="G49" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+G$47)/($C49-G$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="H49" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+H$47)/($C49-H$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="35">
-        <f>$D$14+0*0.01</f>
-        <v/>
-      </c>
-      <c r="D50" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+D$47)/($C50-D$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="E50" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+E$47)/($C50-E$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="F50" s="9">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+F$47)/($C50-F$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="G50" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+G$47)/($C50-G$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="H50" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+H$47)/($C50-H$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="35">
-        <f>$D$14+1*0.01</f>
-        <v/>
-      </c>
-      <c r="D51" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+D$47)/($C51-D$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="E51" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+E$47)/($C51-E$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+F$47)/($C51-F$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="G51" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+G$47)/($C51-G$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="H51" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+H$47)/($C51-H$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" s="35">
-        <f>$D$14+2*0.01</f>
-        <v/>
-      </c>
-      <c r="D52" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+D$47)/($C52-D$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="E52" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+E$47)/($C52-E$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+F$47)/($C52-F$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="G52" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+G$47)/($C52-G$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-      <c r="H52" s="10">
-        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+H$47)/($C52-H$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7115,52 +5789,52 @@
           <t>Vale (VALE3)</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Mineração</t>
         </is>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="33" t="n">
         <v>67.64</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="34" t="n">
         <v>275454.8362</v>
       </c>
-      <c r="F5" s="38" t="n">
+      <c r="F5" s="34" t="n">
         <v>68192</v>
       </c>
-      <c r="G5" s="38" t="n">
+      <c r="G5" s="34" t="n">
         <v>4832</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="34">
         <f>E5+F5+G5</f>
         <v/>
       </c>
-      <c r="I5" s="38" t="n">
+      <c r="I5" s="34" t="n">
         <v>51933</v>
       </c>
-      <c r="J5" s="38" t="n">
+      <c r="J5" s="34" t="n">
         <v>34110</v>
       </c>
-      <c r="K5" s="38" t="n">
+      <c r="K5" s="34" t="n">
         <v>10369</v>
       </c>
-      <c r="L5" s="38" t="n">
+      <c r="L5" s="34" t="n">
         <v>196635</v>
       </c>
-      <c r="M5" s="39">
+      <c r="M5" s="35">
         <f>H5/I5</f>
         <v/>
       </c>
-      <c r="N5" s="39">
+      <c r="N5" s="35">
         <f>H5/J5</f>
         <v/>
       </c>
-      <c r="O5" s="39">
+      <c r="O5" s="35">
         <f>IF(K5&gt;0,E5/K5,"n.a.")</f>
         <v/>
       </c>
-      <c r="P5" s="39">
+      <c r="P5" s="35">
         <f>E5/L5</f>
         <v/>
       </c>
@@ -7171,52 +5845,52 @@
           <t>CSN (CSNA3)</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Siderurgia</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="33" t="n">
         <v>6.36</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="34" t="n">
         <v>8433.9575</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="34" t="n">
         <v>39079.806</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="34" t="n">
         <v>3074.044</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="34">
         <f>E6+F6+G6</f>
         <v/>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="34" t="n">
         <v>7727.263</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="34" t="n">
         <v>3345.416</v>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K6" s="34" t="n">
         <v>-2626.882</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="34" t="n">
         <v>12166.332</v>
       </c>
-      <c r="M6" s="39">
+      <c r="M6" s="35">
         <f>H6/I6</f>
         <v/>
       </c>
-      <c r="N6" s="39">
+      <c r="N6" s="35">
         <f>H6/J6</f>
         <v/>
       </c>
-      <c r="O6" s="39">
+      <c r="O6" s="35">
         <f>IF(K6&gt;0,E6/K6,"n.a.")</f>
         <v/>
       </c>
-      <c r="P6" s="39">
+      <c r="P6" s="35">
         <f>E6/L6</f>
         <v/>
       </c>
@@ -7227,52 +5901,52 @@
           <t>Gerdau (GGBR4)</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Siderurgia</t>
         </is>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="33" t="n">
         <v>24.77</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="34" t="n">
         <v>46089.0479</v>
       </c>
-      <c r="F7" s="38" t="n">
+      <c r="F7" s="34" t="n">
         <v>8117.595</v>
       </c>
-      <c r="G7" s="38" t="n">
+      <c r="G7" s="34" t="n">
         <v>190.194</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="34">
         <f>E7+F7+G7</f>
         <v/>
       </c>
-      <c r="I7" s="38" t="n">
+      <c r="I7" s="34" t="n">
         <v>8730.516</v>
       </c>
-      <c r="J7" s="38" t="n">
+      <c r="J7" s="34" t="n">
         <v>5034.141</v>
       </c>
-      <c r="K7" s="38" t="n">
+      <c r="K7" s="34" t="n">
         <v>2237.081</v>
       </c>
-      <c r="L7" s="38" t="n">
+      <c r="L7" s="34" t="n">
         <v>53544.554</v>
       </c>
-      <c r="M7" s="39">
+      <c r="M7" s="35">
         <f>H7/I7</f>
         <v/>
       </c>
-      <c r="N7" s="39">
+      <c r="N7" s="35">
         <f>H7/J7</f>
         <v/>
       </c>
-      <c r="O7" s="39">
+      <c r="O7" s="35">
         <f>IF(K7&gt;0,E7/K7,"n.a.")</f>
         <v/>
       </c>
-      <c r="P7" s="39">
+      <c r="P7" s="35">
         <f>E7/L7</f>
         <v/>
       </c>
@@ -7283,52 +5957,52 @@
           <t>Usiminas (USIM5)</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t>Siderurgia</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="33" t="n">
         <v>7.21</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="34" t="n">
         <v>8625.687900000001</v>
       </c>
-      <c r="F8" s="38" t="n">
+      <c r="F8" s="34" t="n">
         <v>-599.249</v>
       </c>
-      <c r="G8" s="38" t="n">
+      <c r="G8" s="34" t="n">
         <v>2893.937</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="34">
         <f>E8+F8+G8</f>
         <v/>
       </c>
-      <c r="I8" s="38" t="n">
+      <c r="I8" s="34" t="n">
         <v>164.986</v>
       </c>
-      <c r="J8" s="38" t="n">
+      <c r="J8" s="34" t="n">
         <v>-982.3099999999999</v>
       </c>
-      <c r="K8" s="38" t="n">
+      <c r="K8" s="34" t="n">
         <v>-2320.418</v>
       </c>
-      <c r="L8" s="38" t="n">
+      <c r="L8" s="34" t="n">
         <v>20751.154</v>
       </c>
-      <c r="M8" s="39">
+      <c r="M8" s="35">
         <f>H8/I8</f>
         <v/>
       </c>
-      <c r="N8" s="39">
+      <c r="N8" s="35">
         <f>H8/J8</f>
         <v/>
       </c>
-      <c r="O8" s="39">
+      <c r="O8" s="35">
         <f>IF(K8&gt;0,E8/K8,"n.a.")</f>
         <v/>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="35">
         <f>E8/L8</f>
         <v/>
       </c>
@@ -7339,52 +6013,52 @@
           <t>CSN Mineração (CMIN3)</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="32" t="inlineStr">
         <is>
           <t>Mineração</t>
         </is>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="33" t="n">
         <v>5.06</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="34" t="n">
         <v>27336.3233</v>
       </c>
-      <c r="F9" s="38" t="n">
+      <c r="F9" s="34" t="n">
         <v>1025.104</v>
       </c>
-      <c r="G9" s="38" t="n">
+      <c r="G9" s="34" t="n">
         <v>0.19</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="34">
         <f>E9+F9+G9</f>
         <v/>
       </c>
-      <c r="I9" s="38" t="n">
+      <c r="I9" s="34" t="n">
         <v>6003.736</v>
       </c>
-      <c r="J9" s="38" t="n">
+      <c r="J9" s="34" t="n">
         <v>4642.024</v>
       </c>
-      <c r="K9" s="38" t="n">
+      <c r="K9" s="34" t="n">
         <v>2333.063</v>
       </c>
-      <c r="L9" s="38" t="n">
+      <c r="L9" s="34" t="n">
         <v>7339.411</v>
       </c>
-      <c r="M9" s="39">
+      <c r="M9" s="35">
         <f>H9/I9</f>
         <v/>
       </c>
-      <c r="N9" s="39">
+      <c r="N9" s="35">
         <f>H9/J9</f>
         <v/>
       </c>
-      <c r="O9" s="39">
+      <c r="O9" s="35">
         <f>IF(K9&gt;0,E9/K9,"n.a.")</f>
         <v/>
       </c>
-      <c r="P9" s="39">
+      <c r="P9" s="35">
         <f>E9/L9</f>
         <v/>
       </c>
@@ -7395,35 +6069,35 @@
           <t>Mediana das comparáveis (sem a empresa)</t>
         </is>
       </c>
-      <c r="M10" s="40">
+      <c r="M10" s="36">
         <f>MEDIAN(M6:M9)</f>
         <v/>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="36">
         <f>MEDIAN(N6:N9)</f>
         <v/>
       </c>
-      <c r="O10" s="40">
+      <c r="O10" s="36">
         <f>MEDIAN(O6:O9)</f>
         <v/>
       </c>
-      <c r="P10" s="40">
+      <c r="P10" s="36">
         <f>MEDIAN(P6:P9)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Preço por ação implícito</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>R$ / ação</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
         <is>
           <t>Como</t>
         </is>
@@ -7435,7 +6109,7 @@
           <t>Pelo EV/EBITDA das comparáveis</t>
         </is>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="33">
         <f>IF(I5&gt;0,(M10*I5-F5-G5)/(E5/D5),"n.a.")</f>
         <v/>
       </c>
@@ -7451,7 +6125,7 @@
           <t>Pelo EV/EBIT das comparáveis</t>
         </is>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="33">
         <f>IF(J5&gt;0,(N10*J5-F5-G5)/(E5/D5),"n.a.")</f>
         <v/>
       </c>
@@ -7467,7 +6141,7 @@
           <t>Pelo P/L das comparáveis</t>
         </is>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="33">
         <f>IF(K5&gt;0,O10*K5/(E5/D5),"n.a.")</f>
         <v/>
       </c>
@@ -7483,7 +6157,7 @@
           <t>Pelo P/VP das comparáveis</t>
         </is>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="33">
         <f>P10*L5/(E5/D5)</f>
         <v/>
       </c>
@@ -7499,7 +6173,7 @@
           <t>Pelo fluxo de caixa descontado (aba DCF)</t>
         </is>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="33">
         <f>'DCF'!$D$30</f>
         <v/>
       </c>
@@ -7515,11 +6189,1170 @@
           <t>Preço de mercado</t>
         </is>
       </c>
-      <c r="C18" s="37">
+      <c r="C18" s="33">
         <f>D5</f>
         <v/>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fluxo de caixa descontado - Vale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>O valor da empresa é a soma dos fluxos de caixa futuros trazidos a valor de hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>R$ milhões</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Fluxo da empresa (FCFF), descontado pelo WACC</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+      <c r="G5" s="27" t="n"/>
+      <c r="H5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>FCFF</t>
+        </is>
+      </c>
+      <c r="D6" s="31">
+        <f>'Projeção'!D31</f>
+        <v/>
+      </c>
+      <c r="E6" s="31">
+        <f>'Projeção'!E31</f>
+        <v/>
+      </c>
+      <c r="F6" s="31">
+        <f>'Projeção'!F31</f>
+        <v/>
+      </c>
+      <c r="G6" s="31">
+        <f>'Projeção'!G31</f>
+        <v/>
+      </c>
+      <c r="H6" s="31">
+        <f>'Projeção'!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Parte do ano que entra no valor</t>
+        </is>
+      </c>
+      <c r="D7" s="38">
+        <f>'Premissas'!$D$43</f>
+        <v/>
+      </c>
+      <c r="E7" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Fim do período (anos desde a data-base)</t>
+        </is>
+      </c>
+      <c r="D8" s="38">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="38">
+        <f>D8+1</f>
+        <v/>
+      </c>
+      <c r="F8" s="38">
+        <f>E8+1</f>
+        <v/>
+      </c>
+      <c r="G8" s="38">
+        <f>F8+1</f>
+        <v/>
+      </c>
+      <c r="H8" s="38">
+        <f>G8+1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Meio do período (quando o caixa entra, em média)</t>
+        </is>
+      </c>
+      <c r="D9" s="38">
+        <f>D8-D7/2</f>
+        <v/>
+      </c>
+      <c r="E9" s="38">
+        <f>E8-E7/2</f>
+        <v/>
+      </c>
+      <c r="F9" s="38">
+        <f>F8-F7/2</f>
+        <v/>
+      </c>
+      <c r="G9" s="38">
+        <f>G8-G7/2</f>
+        <v/>
+      </c>
+      <c r="H9" s="38">
+        <f>H8-H7/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Fator de desconto</t>
+        </is>
+      </c>
+      <c r="D10" s="39">
+        <f>1/(1+'WACC'!$D$23)^D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
+        <f>1/(1+'WACC'!$D$23)^E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="39">
+        <f>1/(1+'WACC'!$D$23)^F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="39">
+        <f>1/(1+'WACC'!$D$23)^G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="39">
+        <f>1/(1+'WACC'!$D$23)^H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Valor presente do fluxo</t>
+        </is>
+      </c>
+      <c r="D11" s="31">
+        <f>D6*D7*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="31">
+        <f>E6*E7*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="31">
+        <f>F6*F7*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="31">
+        <f>G6*G7*G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="31">
+        <f>H6*H7*H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Perpetuidade (Gordon)</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="27" t="n"/>
+      <c r="H13" s="27" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="D14" s="11">
+        <f>'WACC'!$D$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Crescimento na perpetuidade (g)</t>
+        </is>
+      </c>
+      <c r="D15" s="11">
+        <f>'Premissas'!$D$37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>FCFF normalizado de 2030</t>
+        </is>
+      </c>
+      <c r="D16" s="12">
+        <f>'Projeção'!H19+'Projeção'!H11-'Premissas'!$D$38*'Projeção'!H11-'Projeção'!H28</f>
+        <v/>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>NOPAT + depreciação - capex de reposição - investimento em giro</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Valor terminal no fim do último ano</t>
+        </is>
+      </c>
+      <c r="D17" s="12">
+        <f>D16*(1+D15)/(D14-D15)</f>
+        <v/>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>FCFF x (1 + g) / (WACC - g)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Valor presente do valor terminal</t>
+        </is>
+      </c>
+      <c r="D18" s="12">
+        <f>D17/(1+D14)^H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Do valor da empresa ao preço por ação</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Valor presente dos fluxos projetados</t>
+        </is>
+      </c>
+      <c r="D21" s="12">
+        <f>SUM($D$11:$H$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>(+) Valor presente do valor terminal</t>
+        </is>
+      </c>
+      <c r="D22" s="12">
+        <f>D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Valor da empresa (Enterprise Value)</t>
+        </is>
+      </c>
+      <c r="D23" s="31">
+        <f>D21+D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>(-) Dívida líquida na data-base</t>
+        </is>
+      </c>
+      <c r="D24" s="12">
+        <f>'Histórico'!K65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>(-) Participação de não controladores</t>
+        </is>
+      </c>
+      <c r="D25" s="12">
+        <f>'Histórico'!K40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>(+) Investimentos em coligadas (valor contábil)</t>
+        </is>
+      </c>
+      <c r="D26" s="12">
+        <f>'Histórico'!K31</f>
+        <v/>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>O FCFF não inclui a equivalência; as coligadas entram pelo valor do balanço.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>(-) Outros passivos tratados como dívida</t>
+        </is>
+      </c>
+      <c r="D27" s="12">
+        <f>'Premissas'!$D$39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Valor do acionista (Equity Value)</t>
+        </is>
+      </c>
+      <c r="D28" s="31">
+        <f>D23-D24-D25+D26-D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Ações em circulação (milhões)</t>
+        </is>
+      </c>
+      <c r="D29" s="40">
+        <f>'Premissas'!$D$44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Preço justo por ação</t>
+        </is>
+      </c>
+      <c r="D30" s="9">
+        <f>D28/D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Preço de mercado</t>
+        </is>
+      </c>
+      <c r="D31" s="10">
+        <f>'Premissas'!$D$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Diferença para o preço de mercado</t>
+        </is>
+      </c>
+      <c r="D32" s="11">
+        <f>D30/D31-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Peso do valor terminal no valor da empresa</t>
+        </is>
+      </c>
+      <c r="D33" s="11">
+        <f>D18/D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>EV / EBITDA 2026E implícito</t>
+        </is>
+      </c>
+      <c r="D34" s="29">
+        <f>D23/'Projeção'!D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>Conferência pelo fluxo do acionista (FCFE), descontado pelo Ke</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="27" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>FCFE</t>
+        </is>
+      </c>
+      <c r="D37" s="31">
+        <f>'Projeção'!D33</f>
+        <v/>
+      </c>
+      <c r="E37" s="31">
+        <f>'Projeção'!E33</f>
+        <v/>
+      </c>
+      <c r="F37" s="31">
+        <f>'Projeção'!F33</f>
+        <v/>
+      </c>
+      <c r="G37" s="31">
+        <f>'Projeção'!G33</f>
+        <v/>
+      </c>
+      <c r="H37" s="31">
+        <f>'Projeção'!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Fator de desconto</t>
+        </is>
+      </c>
+      <c r="D38" s="39">
+        <f>1/(1+'WACC'!$D$24)^D9</f>
+        <v/>
+      </c>
+      <c r="E38" s="39">
+        <f>1/(1+'WACC'!$D$24)^E9</f>
+        <v/>
+      </c>
+      <c r="F38" s="39">
+        <f>1/(1+'WACC'!$D$24)^F9</f>
+        <v/>
+      </c>
+      <c r="G38" s="39">
+        <f>1/(1+'WACC'!$D$24)^G9</f>
+        <v/>
+      </c>
+      <c r="H38" s="39">
+        <f>1/(1+'WACC'!$D$24)^H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Valor presente do fluxo</t>
+        </is>
+      </c>
+      <c r="D39" s="12">
+        <f>D37*D7*D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="12">
+        <f>E37*E7*E38</f>
+        <v/>
+      </c>
+      <c r="F39" s="12">
+        <f>F37*F7*F38</f>
+        <v/>
+      </c>
+      <c r="G39" s="12">
+        <f>G37*G7*G38</f>
+        <v/>
+      </c>
+      <c r="H39" s="12">
+        <f>H37*H7*H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Custo do capital próprio (Ke)</t>
+        </is>
+      </c>
+      <c r="D40" s="11">
+        <f>'WACC'!$D$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>FCFE normalizado de 2030</t>
+        </is>
+      </c>
+      <c r="D41" s="12">
+        <f>'Projeção'!H18-'Projeção'!H9+'Projeção'!H11-'Premissas'!$D$38*'Projeção'!H11-'Projeção'!H28+'Projeção'!H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Valor presente do valor terminal</t>
+        </is>
+      </c>
+      <c r="D42" s="12">
+        <f>D41*(1+D15)/(D40-D15)/(1+D40)^H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Valor do acionista pelo FCFE</t>
+        </is>
+      </c>
+      <c r="D43" s="31">
+        <f>SUM($D$39:$H$39)+D42-D25+D26-D27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Preço por ação pelo FCFE</t>
+        </is>
+      </c>
+      <c r="D44" s="10">
+        <f>D43/D29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>Sensibilidade do preço justo: WACC (linhas) x crescimento perpétuo (colunas)</t>
+        </is>
+      </c>
+      <c r="C46" s="27" t="n"/>
+      <c r="D46" s="27" t="n"/>
+      <c r="E46" s="27" t="n"/>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
+      <c r="H46" s="27" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>WACC \ g</t>
+        </is>
+      </c>
+      <c r="D47" s="41">
+        <f>$D$15+-2*0.005</f>
+        <v/>
+      </c>
+      <c r="E47" s="41">
+        <f>$D$15+-1*0.005</f>
+        <v/>
+      </c>
+      <c r="F47" s="41">
+        <f>$D$15+0*0.005</f>
+        <v/>
+      </c>
+      <c r="G47" s="41">
+        <f>$D$15+1*0.005</f>
+        <v/>
+      </c>
+      <c r="H47" s="41">
+        <f>$D$15+2*0.005</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="41">
+        <f>$D$14+-2*0.01</f>
+        <v/>
+      </c>
+      <c r="D48" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+D$47)/($C48-D$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="E48" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+E$47)/($C48-E$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+F$47)/($C48-F$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="G48" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+G$47)/($C48-G$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="H48" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C48)^$D$9:$H$9)+$D$16*(1+H$47)/($C48-H$47)/(1+$C48)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="41">
+        <f>$D$14+-1*0.01</f>
+        <v/>
+      </c>
+      <c r="D49" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+D$47)/($C49-D$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="E49" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+E$47)/($C49-E$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+F$47)/($C49-F$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="G49" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+G$47)/($C49-G$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="H49" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C49)^$D$9:$H$9)+$D$16*(1+H$47)/($C49-H$47)/(1+$C49)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="41">
+        <f>$D$14+0*0.01</f>
+        <v/>
+      </c>
+      <c r="D50" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+D$47)/($C50-D$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="E50" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+E$47)/($C50-E$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="F50" s="9">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+F$47)/($C50-F$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="G50" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+G$47)/($C50-G$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="H50" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C50)^$D$9:$H$9)+$D$16*(1+H$47)/($C50-H$47)/(1+$C50)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="41">
+        <f>$D$14+1*0.01</f>
+        <v/>
+      </c>
+      <c r="D51" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+D$47)/($C51-D$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="E51" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+E$47)/($C51-E$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+F$47)/($C51-F$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="G51" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+G$47)/($C51-G$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="H51" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C51)^$D$9:$H$9)+$D$16*(1+H$47)/($C51-H$47)/(1+$C51)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="41">
+        <f>$D$14+2*0.01</f>
+        <v/>
+      </c>
+      <c r="D52" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+D$47)/($C52-D$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="E52" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+E$47)/($C52-E$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+F$47)/($C52-F$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="G52" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+G$47)/($C52-G$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+      <c r="H52" s="10">
+        <f>(SUMPRODUCT($D$6:$H$6*$D$7:$H$7/(1+$C52)^$D$9:$H$9)+$D$16*(1+H$47)/($C52-H$47)/(1+$C52)^$H$8-$D$24-$D$25+$D$26-$D$27)/$D$29</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Custo de capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CAPM para o capital próprio; WACC é a média com o custo da dívida depois do imposto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Capital próprio (CAPM)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Juro sem risco (Rf)</t>
+        </is>
+      </c>
+      <c r="D5" s="11">
+        <f>'Premissas'!$D$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D6" s="30">
+        <f>'Premissas'!$D$33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Prêmio de risco de mercado</t>
+        </is>
+      </c>
+      <c r="D7" s="11">
+        <f>'Premissas'!$D$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Prêmio adicional</t>
+        </is>
+      </c>
+      <c r="D8" s="11">
+        <f>'Premissas'!$D$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Custo do capital próprio (Ke)</t>
+        </is>
+      </c>
+      <c r="D9" s="42">
+        <f>D5+D6*D7+D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Ke = Rf + beta x prêmio de mercado + prêmio adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Dívida</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Custo da dívida antes do imposto (Kd)</t>
+        </is>
+      </c>
+      <c r="D12" s="11">
+        <f>'Premissas'!$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Alíquota de IR e CSLL</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>'Premissas'!$D$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Custo da dívida após o imposto</t>
+        </is>
+      </c>
+      <c r="D14" s="42">
+        <f>D12*(1-D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Juro é dedutível: Kd x (1 - alíquota)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Média ponderada</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Peso da dívida</t>
+        </is>
+      </c>
+      <c r="D17" s="11">
+        <f>'Premissas'!$D$36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Peso do capital próprio</t>
+        </is>
+      </c>
+      <c r="D18" s="11">
+        <f>1-D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>WACC pelo CAPM</t>
+        </is>
+      </c>
+      <c r="D19" s="42">
+        <f>D9*D18+D14*D17</f>
+        <v/>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>WACC = Ke x peso do capital próprio + Kd após imposto x peso da dívida</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Cenário</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Ajuste do cenário (pontos sobre o CAPM)</t>
+        </is>
+      </c>
+      <c r="D22" s="43">
+        <f>'Premissas'!$C$10</f>
+        <v/>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Da aba Premissas: zero no moderado, positivo no pessimista, negativo no otimista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>WACC em uso</t>
+        </is>
+      </c>
+      <c r="D23" s="14">
+        <f>D19+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>É a taxa que desconta o fluxo da empresa (FCFF) na aba DCF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Ke em uso</t>
+        </is>
+      </c>
+      <c r="D24" s="11">
+        <f>D9+D22</f>
+        <v/>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>O mesmo ajuste no custo do capital próprio, que desconta o FCFE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Referência: estrutura a valor de mercado</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Conta</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Valor de mercado (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D27" s="12">
+        <f>'Premissas'!$D$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Dívida bruta na data-base (R$ milhões)</t>
+        </is>
+      </c>
+      <c r="D28" s="12">
+        <f>'Histórico'!K64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Peso da dívida a valor de mercado</t>
+        </is>
+      </c>
+      <c r="D29" s="11">
+        <f>D28/(D28+D27)</f>
+        <v/>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Compare com o peso usado acima.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7532,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H36"/>
+  <dimension ref="B1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7556,7 +7389,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Troque o cenário na aba Premissas (célula D4): tudo abaixo e o resto da planilha seguem.</t>
+          <t>Troque o cenário na aba Premissas (célula D4) ou ajuste uma variável à mão: tudo abaixo e o resto da planilha seguem.</t>
         </is>
       </c>
     </row>
@@ -7605,17 +7438,17 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Entradas (cash in)</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n"/>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="25" t="n"/>
-      <c r="G7" s="25" t="n"/>
-      <c r="H7" s="25" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
+      <c r="E7" s="27" t="n"/>
+      <c r="F7" s="27" t="n"/>
+      <c r="G7" s="27" t="n"/>
+      <c r="H7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -7624,23 +7457,23 @@
         </is>
       </c>
       <c r="D8" s="12">
-        <f>'Projeção'!D12-'Projeção'!D11</f>
+        <f>'Projeção'!D10-'Projeção'!D9</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>'Projeção'!E12-'Projeção'!E11</f>
+        <f>'Projeção'!E10-'Projeção'!E9</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>'Projeção'!F12-'Projeção'!F11</f>
+        <f>'Projeção'!F10-'Projeção'!F9</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>'Projeção'!G12-'Projeção'!G11</f>
+        <f>'Projeção'!G10-'Projeção'!G9</f>
         <v/>
       </c>
       <c r="H8" s="12">
-        <f>'Projeção'!H12-'Projeção'!H11</f>
+        <f>'Projeção'!H10-'Projeção'!H9</f>
         <v/>
       </c>
     </row>
@@ -7651,23 +7484,23 @@
         </is>
       </c>
       <c r="D9" s="12">
-        <f>'Projeção'!C38*'Premissas'!$D$44</f>
+        <f>'Projeção'!C38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="E9" s="12">
-        <f>'Projeção'!D38*'Premissas'!$D$44</f>
+        <f>'Projeção'!D38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>'Projeção'!E38*'Premissas'!$D$44</f>
+        <f>'Projeção'!E38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="G9" s="12">
-        <f>'Projeção'!F38*'Premissas'!$D$44</f>
+        <f>'Projeção'!F38*'Premissas'!$D$30</f>
         <v/>
       </c>
       <c r="H9" s="12">
-        <f>'Projeção'!G38*'Premissas'!$D$44</f>
+        <f>'Projeção'!G38*'Premissas'!$D$30</f>
         <v/>
       </c>
     </row>
@@ -7704,39 +7537,39 @@
           <t>Total de entradas</t>
         </is>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="31">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="31">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="31">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="31">
         <f>G8+G9+G10</f>
         <v/>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="31">
         <f>H8+H9+H10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Saídas (cash out)</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="25" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="27" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
@@ -7826,23 +7659,23 @@
         </is>
       </c>
       <c r="D16" s="12">
-        <f>'Projeção'!C42*'Premissas'!$D$43</f>
+        <f>'Projeção'!C42*'Premissas'!$D$29</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>'Projeção'!D42*'Premissas'!$D$43</f>
+        <f>'Projeção'!D42*'Premissas'!$D$29</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>'Projeção'!E42*'Premissas'!$D$43</f>
+        <f>'Projeção'!E42*'Premissas'!$D$29</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>'Projeção'!F42*'Premissas'!$D$43</f>
+        <f>'Projeção'!F42*'Premissas'!$D$29</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>'Projeção'!G42*'Premissas'!$D$43</f>
+        <f>'Projeção'!G42*'Premissas'!$D$29</f>
         <v/>
       </c>
     </row>
@@ -7906,39 +7739,39 @@
           <t>Total de saídas</t>
         </is>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="31">
         <f>SUM(D13:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="31">
         <f>SUM(E13:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="31">
         <f>SUM(F13:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="31">
         <f>SUM(G13:G18)</f>
         <v/>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="31">
         <f>SUM(H13:H18)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="27" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="8" t="inlineStr">
@@ -7946,23 +7779,23 @@
           <t>Entradas - saídas</t>
         </is>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="31">
         <f>D11-D19</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="31">
         <f>E11-E19</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="31">
         <f>F11-F19</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="31">
         <f>G11-G19</f>
         <v/>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="31">
         <f>H11-H19</f>
         <v/>
       </c>
@@ -8022,23 +7855,23 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Comparativo dos cenários (calculado pelo modelo)</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr"/>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr"/>
+      <c r="D26" s="37" t="inlineStr">
         <is>
           <t>Pessimista</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="F26" s="34" t="inlineStr">
+      <c r="E26" s="37" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Otimista</t>
         </is>
@@ -8051,13 +7884,13 @@
         </is>
       </c>
       <c r="D27" s="10" t="n">
-        <v>47.92739610468529</v>
+        <v>51.04899605214507</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>60.98814723086956</v>
+        <v>84.06938824032076</v>
       </c>
       <c r="F27" s="10" t="n">
-        <v>74.04889835705383</v>
+        <v>138.6113563532069</v>
       </c>
     </row>
     <row r="28">
@@ -8067,13 +7900,13 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>240953.8983652528</v>
+        <v>253666.1958568898</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>294142.0571859874</v>
+        <v>388137.3183106821</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>347330.2160067219</v>
+        <v>610252.1748266838</v>
       </c>
     </row>
     <row r="29">
@@ -8083,98 +7916,114 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>195177.8983652528</v>
+        <v>207890.1958568898</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>248366.0571859874</v>
+        <v>342361.3183106821</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>301554.2160067219</v>
+        <v>564476.1748266838</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Receita 2030E</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>240792.8274603522</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>252917.3404241161</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>265041.8533878801</v>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>0.15675595075</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0.14115595075</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>0.12555595075</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Margem EBITDA 2030E</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>0.3081508968721596</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>0.3379567023912316</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0.3650355357676619</v>
+          <t>Receita 2030E</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>218059.1355</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>252946.6612928069</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>284018.8728481748</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caixa no fim de 2030E</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>6737.127389205847</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>8566.806346636517</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>10396.48530406717</v>
+          <t>Margem EBITDA 2030E</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>0.4542</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
+          <t>Caixa no fim de 2030E</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>32462.27018311575</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>30650.84178401469</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>33287.55626904166</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Dívida líquida / EBITDA 2030E</t>
         </is>
       </c>
-      <c r="D33" s="26" t="n">
-        <v>1.303493090422518</v>
-      </c>
-      <c r="E33" s="26" t="n">
-        <v>1.110149998845443</v>
-      </c>
-      <c r="F33" s="26" t="n">
-        <v>0.961868817693069</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Preço justo na planilha viva, no cenário em uso</t>
-        </is>
-      </c>
-      <c r="D35" s="9">
-        <f>'DCF'!$D$30</f>
-        <v/>
+      <c r="D34" s="29" t="n">
+        <v>0.934487891463087</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>0.7312806364869087</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>0.543943390811722</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diferença para o comparativo acima (zero se as premissas não mudaram)</t>
-        </is>
-      </c>
-      <c r="D36" s="27">
-        <f>ROUND(D35-INDEX(D27:F27,'Premissas'!$D$5),2)</f>
+          <t>Preço justo na planilha viva, no cenário em uso</t>
+        </is>
+      </c>
+      <c r="D36" s="9">
+        <f>'DCF'!$D$30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Diferença para o comparativo acima (zero sem ajuste manual)</t>
+        </is>
+      </c>
+      <c r="D37" s="30">
+        <f>IF(COUNT('Premissas'!$H$8:$H$10)=0,ROUND(D36-INDEX(D27:F27,'Premissas'!$D$5),2),"-")</f>
         <v/>
       </c>
     </row>
